--- a/adj mat/sleepy_FCPreProc.xlsx
+++ b/adj mat/sleepy_FCPreProc.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12631" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="25295" uniqueCount="475">
   <si>
     <t>path</t>
   </si>
@@ -628,6 +628,816 @@
   </si>
   <si>
     <t>INET168</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-6/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-8/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-12/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-13/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-15/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-16/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-22/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-23/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-25/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-26/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-28/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET003/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET003/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET003/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET003/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET005/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET005/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET005/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET005/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET010/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET010/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET010/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET010/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET016/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET016/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET018/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET018/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET034/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET034/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET034/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET034/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET036/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET036/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET036/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET036/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET041/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET041/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET041/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET041/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET046/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET046/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET046/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET048/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET048/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET048/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET048/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET049/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET049/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET049/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET049/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET052/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET052/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET052/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET052/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET053/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET058/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET059/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET059/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET061/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET063/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET063/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET063/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET069/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET069/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET069/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET069/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET071/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET071/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET071/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET080/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET080/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET080/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET083/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET084/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET084/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET087/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET087/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET087/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET088/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET088/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET091/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET091/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET105/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET105/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET105/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET105/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET111/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET111/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET111/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET111/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET116/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET160/ses-2/func/</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-5/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-7/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-11/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-14/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-17/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-18/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/networks-pm/replica/pm/derivatives/FCProc-24.1.1/sub-1/ses-20/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET001/ses-5/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET002/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET019/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET019/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET019/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET032/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET032/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET035/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET035/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET035/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET039/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET040/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET040/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET040/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET044/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET045/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET047/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET047/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET050/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET051/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET053/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET053/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET055/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET055/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET057/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET057/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET057/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET058/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET063/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET065/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET067/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET067/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET068/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET070/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET077/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET077/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET077/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET083/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET083/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET084/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET085/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET085/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET085/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET086/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET086/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET088/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET088/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET091/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET093/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET094/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET094/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET096/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET096/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET096/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET098/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET098/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET098/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET099/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET101/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET103/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET104/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET104/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET104/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET106/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET106/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET107/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET108/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET108/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET109/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET109/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET110/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET110/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET120/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET123/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET123/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET123/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET131/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET131/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET133/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET136/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET137/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET137/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET140/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET140/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET141/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET141/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET141/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET156/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET156/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET156/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET158/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET159/ses-4/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-1/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-2/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-3/func/</t>
+  </si>
+  <si>
+    <t>/Volumes/illinois-las-psych-gratton/iNetworks/Nifti/derivatives/preproc_FCProc-24.1.1/sub-INET168/ses-4/func/</t>
   </si>
 </sst>
 </file>
@@ -678,7 +1488,7 @@
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="true"/>
     <col min="2" max="2" width="7.7109375" customWidth="true"/>
-    <col min="3" max="3" width="99.140625" customWidth="true"/>
+    <col min="3" max="3" width="101.5703125" customWidth="true"/>
     <col min="4" max="4" width="7.28515625" customWidth="true"/>
     <col min="5" max="5" width="4.140625" customWidth="true"/>
   </cols>
@@ -704,11 +1514,11 @@
       <c r="A2" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="0">
-        <v>1</v>
+      <c r="B2" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>162</v>
+        <v>329</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>158</v>
@@ -719,11 +1529,11 @@
       <c r="A3" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="0">
-        <v>5</v>
+      <c r="B3" s="0" t="s">
+        <v>323</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>162</v>
+        <v>330</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>158</v>
@@ -734,11 +1544,11 @@
       <c r="A4" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="0">
-        <v>7</v>
+      <c r="B4" s="0" t="s">
+        <v>321</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>162</v>
+        <v>331</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>158</v>
@@ -749,11 +1559,11 @@
       <c r="A5" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="0">
-        <v>11</v>
+      <c r="B5" s="0" t="s">
+        <v>324</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>162</v>
+        <v>332</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>158</v>
@@ -764,11 +1574,11 @@
       <c r="A6" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="0">
-        <v>14</v>
+      <c r="B6" s="0" t="s">
+        <v>325</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>162</v>
+        <v>333</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>158</v>
@@ -779,11 +1589,11 @@
       <c r="A7" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="0">
-        <v>17</v>
+      <c r="B7" s="0" t="s">
+        <v>326</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>162</v>
+        <v>334</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>158</v>
@@ -794,11 +1604,11 @@
       <c r="A8" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B8" s="0">
-        <v>18</v>
+      <c r="B8" s="0" t="s">
+        <v>327</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>162</v>
+        <v>335</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>158</v>
@@ -809,11 +1619,11 @@
       <c r="A9" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="0">
-        <v>20</v>
+      <c r="B9" s="0" t="s">
+        <v>328</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>162</v>
+        <v>336</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>158</v>
@@ -824,11 +1634,11 @@
       <c r="A10" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B10" s="0">
-        <v>1</v>
+      <c r="B10" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>158</v>
@@ -841,11 +1651,11 @@
       <c r="A11" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="0">
-        <v>1</v>
+      <c r="B11" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>158</v>
@@ -858,11 +1668,11 @@
       <c r="A12" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="0">
-        <v>1</v>
+      <c r="B12" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>158</v>
@@ -875,11 +1685,11 @@
       <c r="A13" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B13" s="0">
-        <v>1</v>
+      <c r="B13" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>158</v>
@@ -892,11 +1702,11 @@
       <c r="A14" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B14" s="0">
-        <v>1</v>
+      <c r="B14" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>158</v>
@@ -909,11 +1719,11 @@
       <c r="A15" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="0">
-        <v>1</v>
+      <c r="B15" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>158</v>
@@ -926,11 +1736,11 @@
       <c r="A16" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="0">
-        <v>2</v>
+      <c r="B16" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>158</v>
@@ -943,11 +1753,11 @@
       <c r="A17" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="0">
-        <v>2</v>
+      <c r="B17" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>158</v>
@@ -960,11 +1770,11 @@
       <c r="A18" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B18" s="0">
-        <v>2</v>
+      <c r="B18" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D18" s="0" t="s">
         <v>158</v>
@@ -977,11 +1787,11 @@
       <c r="A19" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="0">
-        <v>2</v>
+      <c r="B19" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>158</v>
@@ -994,11 +1804,11 @@
       <c r="A20" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="0">
-        <v>2</v>
+      <c r="B20" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>158</v>
@@ -1011,11 +1821,11 @@
       <c r="A21" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="0">
-        <v>2</v>
+      <c r="B21" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>158</v>
@@ -1028,11 +1838,11 @@
       <c r="A22" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="0">
-        <v>2</v>
+      <c r="B22" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>162</v>
+        <v>338</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>158</v>
@@ -1045,11 +1855,11 @@
       <c r="A23" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="0">
-        <v>3</v>
+      <c r="B23" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>158</v>
@@ -1062,11 +1872,11 @@
       <c r="A24" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B24" s="0">
-        <v>3</v>
+      <c r="B24" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>158</v>
@@ -1079,11 +1889,11 @@
       <c r="A25" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B25" s="0">
-        <v>3</v>
+      <c r="B25" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>158</v>
@@ -1096,11 +1906,11 @@
       <c r="A26" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="0">
-        <v>3</v>
+      <c r="B26" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>158</v>
@@ -1113,11 +1923,11 @@
       <c r="A27" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="0">
-        <v>3</v>
+      <c r="B27" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>158</v>
@@ -1130,11 +1940,11 @@
       <c r="A28" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B28" s="0">
-        <v>3</v>
+      <c r="B28" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>158</v>
@@ -1147,11 +1957,11 @@
       <c r="A29" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="0">
-        <v>3</v>
+      <c r="B29" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>158</v>
@@ -1164,11 +1974,11 @@
       <c r="A30" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B30" s="0">
-        <v>4</v>
+      <c r="B30" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>158</v>
@@ -1181,11 +1991,11 @@
       <c r="A31" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B31" s="0">
-        <v>4</v>
+      <c r="B31" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>158</v>
@@ -1198,11 +2008,11 @@
       <c r="A32" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="0">
-        <v>4</v>
+      <c r="B32" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>158</v>
@@ -1215,11 +2025,11 @@
       <c r="A33" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="0">
-        <v>4</v>
+      <c r="B33" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>158</v>
@@ -1232,11 +2042,11 @@
       <c r="A34" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B34" s="0">
-        <v>4</v>
+      <c r="B34" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>158</v>
@@ -1249,11 +2059,11 @@
       <c r="A35" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B35" s="0">
-        <v>4</v>
+      <c r="B35" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>158</v>
@@ -1266,11 +2076,11 @@
       <c r="A36" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B36" s="0">
-        <v>5</v>
+      <c r="B36" s="0" t="s">
+        <v>323</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>162</v>
+        <v>341</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>158</v>
@@ -1283,11 +2093,11 @@
       <c r="A37" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B37" s="0">
-        <v>5</v>
+      <c r="B37" s="0" t="s">
+        <v>323</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>162</v>
+        <v>341</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>158</v>
@@ -1300,11 +2110,11 @@
       <c r="A38" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="0">
-        <v>5</v>
+      <c r="B38" s="0" t="s">
+        <v>323</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>162</v>
+        <v>341</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>158</v>
@@ -1317,11 +2127,11 @@
       <c r="A39" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="0">
-        <v>5</v>
+      <c r="B39" s="0" t="s">
+        <v>323</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>162</v>
+        <v>341</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>158</v>
@@ -1334,11 +2144,11 @@
       <c r="A40" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="0">
-        <v>1</v>
+      <c r="B40" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>158</v>
@@ -1351,11 +2161,11 @@
       <c r="A41" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="0">
-        <v>1</v>
+      <c r="B41" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>158</v>
@@ -1368,11 +2178,11 @@
       <c r="A42" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B42" s="0">
-        <v>1</v>
+      <c r="B42" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>158</v>
@@ -1385,11 +2195,11 @@
       <c r="A43" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B43" s="0">
-        <v>1</v>
+      <c r="B43" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>158</v>
@@ -1402,11 +2212,11 @@
       <c r="A44" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="0">
-        <v>2</v>
+      <c r="B44" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>158</v>
@@ -1419,11 +2229,11 @@
       <c r="A45" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B45" s="0">
-        <v>2</v>
+      <c r="B45" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>158</v>
@@ -1436,11 +2246,11 @@
       <c r="A46" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="0">
-        <v>2</v>
+      <c r="B46" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>158</v>
@@ -1453,11 +2263,11 @@
       <c r="A47" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B47" s="0">
-        <v>2</v>
+      <c r="B47" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>158</v>
@@ -1470,11 +2280,11 @@
       <c r="A48" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B48" s="0">
-        <v>2</v>
+      <c r="B48" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>158</v>
@@ -1487,11 +2297,11 @@
       <c r="A49" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B49" s="0">
-        <v>3</v>
+      <c r="B49" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>158</v>
@@ -1504,11 +2314,11 @@
       <c r="A50" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="B50" s="0">
-        <v>1</v>
+      <c r="B50" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D50" s="0" t="s">
         <v>158</v>
@@ -1521,11 +2331,11 @@
       <c r="A51" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="B51" s="0">
-        <v>4</v>
+      <c r="B51" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="D51" s="0" t="s">
         <v>158</v>
@@ -1538,11 +2348,11 @@
       <c r="A52" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="0">
-        <v>4</v>
+      <c r="B52" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>158</v>
@@ -1555,11 +2365,11 @@
       <c r="A53" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="0">
-        <v>2</v>
+      <c r="B53" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>162</v>
+        <v>245</v>
       </c>
       <c r="D53" s="0" t="s">
         <v>158</v>
@@ -1572,11 +2382,11 @@
       <c r="A54" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="0">
-        <v>4</v>
+      <c r="B54" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="D54" s="0" t="s">
         <v>158</v>
@@ -1589,11 +2399,11 @@
       <c r="A55" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B55" s="0">
-        <v>2</v>
+      <c r="B55" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>162</v>
+        <v>343</v>
       </c>
       <c r="D55" s="0" t="s">
         <v>158</v>
@@ -1606,11 +2416,11 @@
       <c r="A56" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B56" s="0">
-        <v>3</v>
+      <c r="B56" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D56" s="0" t="s">
         <v>158</v>
@@ -1623,11 +2433,11 @@
       <c r="A57" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="0">
-        <v>3</v>
+      <c r="B57" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D57" s="0" t="s">
         <v>158</v>
@@ -1640,11 +2450,11 @@
       <c r="A58" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B58" s="0">
-        <v>3</v>
+      <c r="B58" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D58" s="0" t="s">
         <v>158</v>
@@ -1657,11 +2467,11 @@
       <c r="A59" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="0">
-        <v>3</v>
+      <c r="B59" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D59" s="0" t="s">
         <v>158</v>
@@ -1674,11 +2484,11 @@
       <c r="A60" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B60" s="0">
-        <v>3</v>
+      <c r="B60" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C60" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D60" s="0" t="s">
         <v>158</v>
@@ -1691,11 +2501,11 @@
       <c r="A61" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="0">
-        <v>3</v>
+      <c r="B61" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C61" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D61" s="0" t="s">
         <v>158</v>
@@ -1708,11 +2518,11 @@
       <c r="A62" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B62" s="0">
-        <v>3</v>
+      <c r="B62" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D62" s="0" t="s">
         <v>158</v>
@@ -1725,11 +2535,11 @@
       <c r="A63" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B63" s="0">
-        <v>3</v>
+      <c r="B63" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>162</v>
+        <v>344</v>
       </c>
       <c r="D63" s="0" t="s">
         <v>158</v>
@@ -1742,11 +2552,11 @@
       <c r="A64" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B64" s="0">
-        <v>4</v>
+      <c r="B64" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D64" s="0" t="s">
         <v>158</v>
@@ -1759,11 +2569,11 @@
       <c r="A65" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B65" s="0">
-        <v>4</v>
+      <c r="B65" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C65" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D65" s="0" t="s">
         <v>158</v>
@@ -1776,11 +2586,11 @@
       <c r="A66" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B66" s="0">
-        <v>4</v>
+      <c r="B66" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D66" s="0" t="s">
         <v>158</v>
@@ -1793,11 +2603,11 @@
       <c r="A67" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B67" s="0">
-        <v>4</v>
+      <c r="B67" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D67" s="0" t="s">
         <v>158</v>
@@ -1810,11 +2620,11 @@
       <c r="A68" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B68" s="0">
-        <v>4</v>
+      <c r="B68" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C68" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D68" s="0" t="s">
         <v>158</v>
@@ -1827,11 +2637,11 @@
       <c r="A69" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B69" s="0">
-        <v>4</v>
+      <c r="B69" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D69" s="0" t="s">
         <v>158</v>
@@ -1844,11 +2654,11 @@
       <c r="A70" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="B70" s="0">
-        <v>4</v>
+      <c r="B70" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>162</v>
+        <v>345</v>
       </c>
       <c r="D70" s="0" t="s">
         <v>158</v>
@@ -1861,11 +2671,11 @@
       <c r="A71" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="B71" s="0">
-        <v>3</v>
+      <c r="B71" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C71" s="0" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>158</v>
@@ -1878,11 +2688,11 @@
       <c r="A72" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="B72" s="0">
-        <v>3</v>
+      <c r="B72" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C72" s="0" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>158</v>
@@ -1895,11 +2705,11 @@
       <c r="A73" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="B73" s="0">
-        <v>3</v>
+      <c r="B73" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>158</v>
@@ -1912,11 +2722,11 @@
       <c r="A74" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="0">
-        <v>4</v>
+      <c r="B74" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>162</v>
+        <v>347</v>
       </c>
       <c r="D74" s="0" t="s">
         <v>158</v>
@@ -1929,11 +2739,11 @@
       <c r="A75" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="0">
-        <v>4</v>
+      <c r="B75" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>162</v>
+        <v>347</v>
       </c>
       <c r="D75" s="0" t="s">
         <v>158</v>
@@ -1946,11 +2756,11 @@
       <c r="A76" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B76" s="0">
-        <v>2</v>
+      <c r="B76" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>162</v>
+        <v>348</v>
       </c>
       <c r="D76" s="0" t="s">
         <v>158</v>
@@ -1963,11 +2773,11 @@
       <c r="A77" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B77" s="0">
-        <v>2</v>
+      <c r="B77" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>162</v>
+        <v>348</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>158</v>
@@ -1980,11 +2790,11 @@
       <c r="A78" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B78" s="0">
-        <v>3</v>
+      <c r="B78" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C78" s="0" t="s">
-        <v>162</v>
+        <v>349</v>
       </c>
       <c r="D78" s="0" t="s">
         <v>158</v>
@@ -1997,11 +2807,11 @@
       <c r="A79" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B79" s="0">
-        <v>3</v>
+      <c r="B79" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C79" s="0" t="s">
-        <v>162</v>
+        <v>349</v>
       </c>
       <c r="D79" s="0" t="s">
         <v>158</v>
@@ -2014,11 +2824,11 @@
       <c r="A80" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="0">
-        <v>4</v>
+      <c r="B80" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>162</v>
+        <v>350</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>158</v>
@@ -2031,11 +2841,11 @@
       <c r="A81" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B81" s="0">
-        <v>4</v>
+      <c r="B81" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>162</v>
+        <v>350</v>
       </c>
       <c r="D81" s="0" t="s">
         <v>158</v>
@@ -2048,11 +2858,11 @@
       <c r="A82" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="0">
-        <v>4</v>
+      <c r="B82" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C82" s="0" t="s">
-        <v>162</v>
+        <v>350</v>
       </c>
       <c r="D82" s="0" t="s">
         <v>158</v>
@@ -2065,11 +2875,11 @@
       <c r="A83" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B83" s="0">
-        <v>1</v>
+      <c r="B83" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D83" s="0" t="s">
         <v>158</v>
@@ -2082,11 +2892,11 @@
       <c r="A84" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B84" s="0">
-        <v>1</v>
+      <c r="B84" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C84" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D84" s="0" t="s">
         <v>158</v>
@@ -2099,11 +2909,11 @@
       <c r="A85" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B85" s="0">
-        <v>1</v>
+      <c r="B85" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C85" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D85" s="0" t="s">
         <v>158</v>
@@ -2116,11 +2926,11 @@
       <c r="A86" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B86" s="0">
-        <v>1</v>
+      <c r="B86" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C86" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D86" s="0" t="s">
         <v>158</v>
@@ -2133,11 +2943,11 @@
       <c r="A87" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="0">
-        <v>1</v>
+      <c r="B87" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C87" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D87" s="0" t="s">
         <v>158</v>
@@ -2150,11 +2960,11 @@
       <c r="A88" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B88" s="0">
-        <v>1</v>
+      <c r="B88" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C88" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D88" s="0" t="s">
         <v>158</v>
@@ -2167,11 +2977,11 @@
       <c r="A89" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B89" s="0">
-        <v>1</v>
+      <c r="B89" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C89" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D89" s="0" t="s">
         <v>158</v>
@@ -2184,11 +2994,11 @@
       <c r="A90" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B90" s="0">
-        <v>1</v>
+      <c r="B90" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="D90" s="0" t="s">
         <v>158</v>
@@ -2201,11 +3011,11 @@
       <c r="A91" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B91" s="0">
-        <v>2</v>
+      <c r="B91" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="D91" s="0" t="s">
         <v>158</v>
@@ -2218,11 +3028,11 @@
       <c r="A92" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B92" s="0">
-        <v>2</v>
+      <c r="B92" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C92" s="0" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="D92" s="0" t="s">
         <v>158</v>
@@ -2235,11 +3045,11 @@
       <c r="A93" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B93" s="0">
-        <v>2</v>
+      <c r="B93" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C93" s="0" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="D93" s="0" t="s">
         <v>158</v>
@@ -2252,11 +3062,11 @@
       <c r="A94" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B94" s="0">
-        <v>2</v>
+      <c r="B94" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C94" s="0" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="D94" s="0" t="s">
         <v>158</v>
@@ -2269,11 +3079,11 @@
       <c r="A95" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B95" s="0">
-        <v>2</v>
+      <c r="B95" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C95" s="0" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="D95" s="0" t="s">
         <v>158</v>
@@ -2286,11 +3096,11 @@
       <c r="A96" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B96" s="0">
-        <v>2</v>
+      <c r="B96" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C96" s="0" t="s">
-        <v>162</v>
+        <v>352</v>
       </c>
       <c r="D96" s="0" t="s">
         <v>158</v>
@@ -2303,11 +3113,11 @@
       <c r="A97" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B97" s="0">
-        <v>3</v>
+      <c r="B97" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C97" s="0" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D97" s="0" t="s">
         <v>158</v>
@@ -2320,11 +3130,11 @@
       <c r="A98" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B98" s="0">
-        <v>3</v>
+      <c r="B98" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C98" s="0" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D98" s="0" t="s">
         <v>158</v>
@@ -2337,11 +3147,11 @@
       <c r="A99" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B99" s="0">
-        <v>3</v>
+      <c r="B99" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C99" s="0" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D99" s="0" t="s">
         <v>158</v>
@@ -2354,11 +3164,11 @@
       <c r="A100" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B100" s="0">
-        <v>3</v>
+      <c r="B100" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C100" s="0" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D100" s="0" t="s">
         <v>158</v>
@@ -2371,11 +3181,11 @@
       <c r="A101" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B101" s="0">
-        <v>3</v>
+      <c r="B101" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D101" s="0" t="s">
         <v>158</v>
@@ -2388,11 +3198,11 @@
       <c r="A102" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B102" s="0">
-        <v>3</v>
+      <c r="B102" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C102" s="0" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D102" s="0" t="s">
         <v>158</v>
@@ -2405,11 +3215,11 @@
       <c r="A103" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B103" s="0">
-        <v>4</v>
+      <c r="B103" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C103" s="0" t="s">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="D103" s="0" t="s">
         <v>158</v>
@@ -2422,11 +3232,11 @@
       <c r="A104" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B104" s="0">
-        <v>4</v>
+      <c r="B104" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C104" s="0" t="s">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="D104" s="0" t="s">
         <v>158</v>
@@ -2439,11 +3249,11 @@
       <c r="A105" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B105" s="0">
-        <v>4</v>
+      <c r="B105" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C105" s="0" t="s">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="D105" s="0" t="s">
         <v>158</v>
@@ -2456,11 +3266,11 @@
       <c r="A106" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B106" s="0">
-        <v>4</v>
+      <c r="B106" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C106" s="0" t="s">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="D106" s="0" t="s">
         <v>158</v>
@@ -2473,11 +3283,11 @@
       <c r="A107" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="B107" s="0">
-        <v>4</v>
+      <c r="B107" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>162</v>
+        <v>354</v>
       </c>
       <c r="D107" s="0" t="s">
         <v>158</v>
@@ -2490,11 +3300,11 @@
       <c r="A108" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B108" s="0">
-        <v>2</v>
+      <c r="B108" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D108" s="0" t="s">
         <v>158</v>
@@ -2507,11 +3317,11 @@
       <c r="A109" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B109" s="0">
-        <v>2</v>
+      <c r="B109" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C109" s="0" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D109" s="0" t="s">
         <v>158</v>
@@ -2524,11 +3334,11 @@
       <c r="A110" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B110" s="0">
-        <v>2</v>
+      <c r="B110" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C110" s="0" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D110" s="0" t="s">
         <v>158</v>
@@ -2541,11 +3351,11 @@
       <c r="A111" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B111" s="0">
-        <v>2</v>
+      <c r="B111" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C111" s="0" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D111" s="0" t="s">
         <v>158</v>
@@ -2558,11 +3368,11 @@
       <c r="A112" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B112" s="0">
-        <v>2</v>
+      <c r="B112" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C112" s="0" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D112" s="0" t="s">
         <v>158</v>
@@ -2575,11 +3385,11 @@
       <c r="A113" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B113" s="0">
-        <v>2</v>
+      <c r="B113" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C113" s="0" t="s">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="D113" s="0" t="s">
         <v>158</v>
@@ -2592,11 +3402,11 @@
       <c r="A114" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B114" s="0">
-        <v>3</v>
+      <c r="B114" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C114" s="0" t="s">
-        <v>162</v>
+        <v>356</v>
       </c>
       <c r="D114" s="0" t="s">
         <v>158</v>
@@ -2609,11 +3419,11 @@
       <c r="A115" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B115" s="0">
-        <v>3</v>
+      <c r="B115" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C115" s="0" t="s">
-        <v>162</v>
+        <v>356</v>
       </c>
       <c r="D115" s="0" t="s">
         <v>158</v>
@@ -2626,11 +3436,11 @@
       <c r="A116" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B116" s="0">
-        <v>3</v>
+      <c r="B116" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C116" s="0" t="s">
-        <v>162</v>
+        <v>356</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>158</v>
@@ -2643,11 +3453,11 @@
       <c r="A117" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B117" s="0">
-        <v>3</v>
+      <c r="B117" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C117" s="0" t="s">
-        <v>162</v>
+        <v>356</v>
       </c>
       <c r="D117" s="0" t="s">
         <v>158</v>
@@ -2660,11 +3470,11 @@
       <c r="A118" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B118" s="0">
-        <v>4</v>
+      <c r="B118" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C118" s="0" t="s">
-        <v>162</v>
+        <v>357</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>158</v>
@@ -2677,11 +3487,11 @@
       <c r="A119" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B119" s="0">
-        <v>4</v>
+      <c r="B119" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C119" s="0" t="s">
-        <v>162</v>
+        <v>357</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>158</v>
@@ -2694,11 +3504,11 @@
       <c r="A120" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B120" s="0">
-        <v>1</v>
+      <c r="B120" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C120" s="0" t="s">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>158</v>
@@ -2711,11 +3521,11 @@
       <c r="A121" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B121" s="0">
-        <v>1</v>
+      <c r="B121" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C121" s="0" t="s">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c r="D121" s="0" t="s">
         <v>158</v>
@@ -2728,11 +3538,11 @@
       <c r="A122" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B122" s="0">
-        <v>1</v>
+      <c r="B122" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C122" s="0" t="s">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c r="D122" s="0" t="s">
         <v>158</v>
@@ -2745,11 +3555,11 @@
       <c r="A123" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B123" s="0">
-        <v>1</v>
+      <c r="B123" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C123" s="0" t="s">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c r="D123" s="0" t="s">
         <v>158</v>
@@ -2762,11 +3572,11 @@
       <c r="A124" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B124" s="0">
-        <v>2</v>
+      <c r="B124" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C124" s="0" t="s">
-        <v>162</v>
+        <v>359</v>
       </c>
       <c r="D124" s="0" t="s">
         <v>158</v>
@@ -2779,11 +3589,11 @@
       <c r="A125" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B125" s="0">
-        <v>2</v>
+      <c r="B125" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C125" s="0" t="s">
-        <v>162</v>
+        <v>359</v>
       </c>
       <c r="D125" s="0" t="s">
         <v>158</v>
@@ -2796,11 +3606,11 @@
       <c r="A126" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B126" s="0">
-        <v>3</v>
+      <c r="B126" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C126" s="0" t="s">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="D126" s="0" t="s">
         <v>158</v>
@@ -2813,11 +3623,11 @@
       <c r="A127" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B127" s="0">
-        <v>3</v>
+      <c r="B127" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C127" s="0" t="s">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="D127" s="0" t="s">
         <v>158</v>
@@ -2830,11 +3640,11 @@
       <c r="A128" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B128" s="0">
-        <v>3</v>
+      <c r="B128" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C128" s="0" t="s">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="D128" s="0" t="s">
         <v>158</v>
@@ -2847,11 +3657,11 @@
       <c r="A129" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B129" s="0">
-        <v>3</v>
+      <c r="B129" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C129" s="0" t="s">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="D129" s="0" t="s">
         <v>158</v>
@@ -2864,11 +3674,11 @@
       <c r="A130" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B130" s="0">
-        <v>4</v>
+      <c r="B130" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C130" s="0" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="D130" s="0" t="s">
         <v>158</v>
@@ -2881,11 +3691,11 @@
       <c r="A131" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B131" s="0">
-        <v>4</v>
+      <c r="B131" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C131" s="0" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="D131" s="0" t="s">
         <v>158</v>
@@ -2898,11 +3708,11 @@
       <c r="A132" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B132" s="0">
-        <v>4</v>
+      <c r="B132" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C132" s="0" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="D132" s="0" t="s">
         <v>158</v>
@@ -2915,11 +3725,11 @@
       <c r="A133" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B133" s="0">
-        <v>4</v>
+      <c r="B133" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C133" s="0" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="D133" s="0" t="s">
         <v>158</v>
@@ -2932,11 +3742,11 @@
       <c r="A134" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="B134" s="0">
-        <v>4</v>
+      <c r="B134" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C134" s="0" t="s">
-        <v>162</v>
+        <v>361</v>
       </c>
       <c r="D134" s="0" t="s">
         <v>158</v>
@@ -2949,11 +3759,11 @@
       <c r="A135" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B135" s="0">
-        <v>1</v>
+      <c r="B135" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C135" s="0" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="D135" s="0" t="s">
         <v>158</v>
@@ -2966,11 +3776,11 @@
       <c r="A136" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B136" s="0">
-        <v>1</v>
+      <c r="B136" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C136" s="0" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="D136" s="0" t="s">
         <v>158</v>
@@ -2983,11 +3793,11 @@
       <c r="A137" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B137" s="0">
-        <v>1</v>
+      <c r="B137" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C137" s="0" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="D137" s="0" t="s">
         <v>158</v>
@@ -3000,11 +3810,11 @@
       <c r="A138" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B138" s="0">
-        <v>1</v>
+      <c r="B138" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C138" s="0" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="D138" s="0" t="s">
         <v>158</v>
@@ -3017,11 +3827,11 @@
       <c r="A139" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B139" s="0">
-        <v>1</v>
+      <c r="B139" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C139" s="0" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="D139" s="0" t="s">
         <v>158</v>
@@ -3034,11 +3844,11 @@
       <c r="A140" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B140" s="0">
-        <v>2</v>
+      <c r="B140" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C140" s="0" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D140" s="0" t="s">
         <v>158</v>
@@ -3051,11 +3861,11 @@
       <c r="A141" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B141" s="0">
-        <v>2</v>
+      <c r="B141" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C141" s="0" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D141" s="0" t="s">
         <v>158</v>
@@ -3068,11 +3878,11 @@
       <c r="A142" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B142" s="0">
-        <v>2</v>
+      <c r="B142" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C142" s="0" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D142" s="0" t="s">
         <v>158</v>
@@ -3085,11 +3895,11 @@
       <c r="A143" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B143" s="0">
-        <v>2</v>
+      <c r="B143" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C143" s="0" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D143" s="0" t="s">
         <v>158</v>
@@ -3102,11 +3912,11 @@
       <c r="A144" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B144" s="0">
-        <v>2</v>
+      <c r="B144" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C144" s="0" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D144" s="0" t="s">
         <v>158</v>
@@ -3119,11 +3929,11 @@
       <c r="A145" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B145" s="0">
-        <v>2</v>
+      <c r="B145" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C145" s="0" t="s">
-        <v>162</v>
+        <v>363</v>
       </c>
       <c r="D145" s="0" t="s">
         <v>158</v>
@@ -3136,11 +3946,11 @@
       <c r="A146" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B146" s="0">
-        <v>3</v>
+      <c r="B146" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D146" s="0" t="s">
         <v>158</v>
@@ -3153,11 +3963,11 @@
       <c r="A147" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B147" s="0">
-        <v>3</v>
+      <c r="B147" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D147" s="0" t="s">
         <v>158</v>
@@ -3170,11 +3980,11 @@
       <c r="A148" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B148" s="0">
-        <v>3</v>
+      <c r="B148" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C148" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D148" s="0" t="s">
         <v>158</v>
@@ -3187,11 +3997,11 @@
       <c r="A149" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B149" s="0">
-        <v>3</v>
+      <c r="B149" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C149" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>158</v>
@@ -3204,11 +4014,11 @@
       <c r="A150" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B150" s="0">
-        <v>3</v>
+      <c r="B150" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C150" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D150" s="0" t="s">
         <v>158</v>
@@ -3221,11 +4031,11 @@
       <c r="A151" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B151" s="0">
-        <v>3</v>
+      <c r="B151" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C151" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D151" s="0" t="s">
         <v>158</v>
@@ -3238,11 +4048,11 @@
       <c r="A152" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B152" s="0">
-        <v>3</v>
+      <c r="B152" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C152" s="0" t="s">
-        <v>162</v>
+        <v>364</v>
       </c>
       <c r="D152" s="0" t="s">
         <v>158</v>
@@ -3255,11 +4065,11 @@
       <c r="A153" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B153" s="0">
-        <v>4</v>
+      <c r="B153" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C153" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D153" s="0" t="s">
         <v>158</v>
@@ -3272,11 +4082,11 @@
       <c r="A154" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B154" s="0">
-        <v>4</v>
+      <c r="B154" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C154" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D154" s="0" t="s">
         <v>158</v>
@@ -3289,11 +4099,11 @@
       <c r="A155" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B155" s="0">
-        <v>4</v>
+      <c r="B155" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C155" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D155" s="0" t="s">
         <v>158</v>
@@ -3306,11 +4116,11 @@
       <c r="A156" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B156" s="0">
-        <v>4</v>
+      <c r="B156" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C156" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D156" s="0" t="s">
         <v>158</v>
@@ -3323,11 +4133,11 @@
       <c r="A157" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B157" s="0">
-        <v>4</v>
+      <c r="B157" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C157" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D157" s="0" t="s">
         <v>158</v>
@@ -3340,11 +4150,11 @@
       <c r="A158" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B158" s="0">
-        <v>4</v>
+      <c r="B158" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C158" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D158" s="0" t="s">
         <v>158</v>
@@ -3357,11 +4167,11 @@
       <c r="A159" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B159" s="0">
-        <v>4</v>
+      <c r="B159" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C159" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D159" s="0" t="s">
         <v>158</v>
@@ -3374,11 +4184,11 @@
       <c r="A160" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B160" s="0">
-        <v>4</v>
+      <c r="B160" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C160" s="0" t="s">
-        <v>162</v>
+        <v>365</v>
       </c>
       <c r="D160" s="0" t="s">
         <v>158</v>
@@ -3391,11 +4201,11 @@
       <c r="A161" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B161" s="0">
-        <v>3</v>
+      <c r="B161" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="D161" s="0" t="s">
         <v>158</v>
@@ -3408,11 +4218,11 @@
       <c r="A162" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B162" s="0">
-        <v>3</v>
+      <c r="B162" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C162" s="0" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="D162" s="0" t="s">
         <v>158</v>
@@ -3425,11 +4235,11 @@
       <c r="A163" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B163" s="0">
-        <v>3</v>
+      <c r="B163" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C163" s="0" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="D163" s="0" t="s">
         <v>158</v>
@@ -3442,11 +4252,11 @@
       <c r="A164" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B164" s="0">
-        <v>3</v>
+      <c r="B164" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C164" s="0" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="D164" s="0" t="s">
         <v>158</v>
@@ -3459,11 +4269,11 @@
       <c r="A165" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B165" s="0">
-        <v>3</v>
+      <c r="B165" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C165" s="0" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="D165" s="0" t="s">
         <v>158</v>
@@ -3476,11 +4286,11 @@
       <c r="A166" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B166" s="0">
-        <v>3</v>
+      <c r="B166" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C166" s="0" t="s">
-        <v>162</v>
+        <v>366</v>
       </c>
       <c r="D166" s="0" t="s">
         <v>158</v>
@@ -3493,11 +4303,11 @@
       <c r="A167" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B167" s="0">
-        <v>4</v>
+      <c r="B167" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C167" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D167" s="0" t="s">
         <v>158</v>
@@ -3510,11 +4320,11 @@
       <c r="A168" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B168" s="0">
-        <v>4</v>
+      <c r="B168" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D168" s="0" t="s">
         <v>158</v>
@@ -3527,11 +4337,11 @@
       <c r="A169" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B169" s="0">
-        <v>4</v>
+      <c r="B169" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D169" s="0" t="s">
         <v>158</v>
@@ -3544,11 +4354,11 @@
       <c r="A170" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B170" s="0">
-        <v>4</v>
+      <c r="B170" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C170" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D170" s="0" t="s">
         <v>158</v>
@@ -3561,11 +4371,11 @@
       <c r="A171" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B171" s="0">
-        <v>4</v>
+      <c r="B171" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C171" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D171" s="0" t="s">
         <v>158</v>
@@ -3578,11 +4388,11 @@
       <c r="A172" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B172" s="0">
-        <v>4</v>
+      <c r="B172" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D172" s="0" t="s">
         <v>158</v>
@@ -3595,11 +4405,11 @@
       <c r="A173" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B173" s="0">
-        <v>4</v>
+      <c r="B173" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C173" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D173" s="0" t="s">
         <v>158</v>
@@ -3612,11 +4422,11 @@
       <c r="A174" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="B174" s="0">
-        <v>4</v>
+      <c r="B174" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C174" s="0" t="s">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="D174" s="0" t="s">
         <v>158</v>
@@ -3629,11 +4439,11 @@
       <c r="A175" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="B175" s="0">
-        <v>1</v>
+      <c r="B175" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C175" s="0" t="s">
-        <v>162</v>
+        <v>271</v>
       </c>
       <c r="D175" s="0" t="s">
         <v>158</v>
@@ -3646,11 +4456,11 @@
       <c r="A176" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="B176" s="0">
-        <v>2</v>
+      <c r="B176" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C176" s="0" t="s">
-        <v>162</v>
+        <v>272</v>
       </c>
       <c r="D176" s="0" t="s">
         <v>158</v>
@@ -3663,11 +4473,11 @@
       <c r="A177" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B177" s="0">
-        <v>1</v>
+      <c r="B177" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C177" s="0" t="s">
-        <v>162</v>
+        <v>368</v>
       </c>
       <c r="D177" s="0" t="s">
         <v>158</v>
@@ -3680,11 +4490,11 @@
       <c r="A178" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B178" s="0">
-        <v>1</v>
+      <c r="B178" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>162</v>
+        <v>368</v>
       </c>
       <c r="D178" s="0" t="s">
         <v>158</v>
@@ -3697,11 +4507,11 @@
       <c r="A179" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B179" s="0">
-        <v>1</v>
+      <c r="B179" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>162</v>
+        <v>368</v>
       </c>
       <c r="D179" s="0" t="s">
         <v>158</v>
@@ -3714,11 +4524,11 @@
       <c r="A180" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B180" s="0">
-        <v>2</v>
+      <c r="B180" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>162</v>
+        <v>369</v>
       </c>
       <c r="D180" s="0" t="s">
         <v>158</v>
@@ -3731,11 +4541,11 @@
       <c r="A181" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B181" s="0">
-        <v>2</v>
+      <c r="B181" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C181" s="0" t="s">
-        <v>162</v>
+        <v>369</v>
       </c>
       <c r="D181" s="0" t="s">
         <v>158</v>
@@ -3748,11 +4558,11 @@
       <c r="A182" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B182" s="0">
-        <v>2</v>
+      <c r="B182" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C182" s="0" t="s">
-        <v>162</v>
+        <v>369</v>
       </c>
       <c r="D182" s="0" t="s">
         <v>158</v>
@@ -3765,11 +4575,11 @@
       <c r="A183" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B183" s="0">
-        <v>2</v>
+      <c r="B183" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C183" s="0" t="s">
-        <v>162</v>
+        <v>369</v>
       </c>
       <c r="D183" s="0" t="s">
         <v>158</v>
@@ -3782,11 +4592,11 @@
       <c r="A184" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B184" s="0">
-        <v>2</v>
+      <c r="B184" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C184" s="0" t="s">
-        <v>162</v>
+        <v>369</v>
       </c>
       <c r="D184" s="0" t="s">
         <v>158</v>
@@ -3799,11 +4609,11 @@
       <c r="A185" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B185" s="0">
-        <v>3</v>
+      <c r="B185" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="D185" s="0" t="s">
         <v>158</v>
@@ -3816,11 +4626,11 @@
       <c r="A186" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B186" s="0">
-        <v>3</v>
+      <c r="B186" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="D186" s="0" t="s">
         <v>158</v>
@@ -3833,11 +4643,11 @@
       <c r="A187" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B187" s="0">
-        <v>3</v>
+      <c r="B187" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>162</v>
+        <v>370</v>
       </c>
       <c r="D187" s="0" t="s">
         <v>158</v>
@@ -3850,11 +4660,11 @@
       <c r="A188" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B188" s="0">
-        <v>4</v>
+      <c r="B188" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="D188" s="0" t="s">
         <v>158</v>
@@ -3867,11 +4677,11 @@
       <c r="A189" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B189" s="0">
-        <v>4</v>
+      <c r="B189" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C189" s="0" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="D189" s="0" t="s">
         <v>158</v>
@@ -3884,11 +4694,11 @@
       <c r="A190" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B190" s="0">
-        <v>4</v>
+      <c r="B190" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C190" s="0" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="D190" s="0" t="s">
         <v>158</v>
@@ -3901,11 +4711,11 @@
       <c r="A191" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B191" s="0">
-        <v>4</v>
+      <c r="B191" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C191" s="0" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="D191" s="0" t="s">
         <v>158</v>
@@ -3918,11 +4728,11 @@
       <c r="A192" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B192" s="0">
-        <v>4</v>
+      <c r="B192" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C192" s="0" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="D192" s="0" t="s">
         <v>158</v>
@@ -3935,11 +4745,11 @@
       <c r="A193" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B193" s="0">
-        <v>1</v>
+      <c r="B193" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C193" s="0" t="s">
-        <v>162</v>
+        <v>372</v>
       </c>
       <c r="D193" s="0" t="s">
         <v>158</v>
@@ -3952,11 +4762,11 @@
       <c r="A194" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B194" s="0">
-        <v>2</v>
+      <c r="B194" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="D194" s="0" t="s">
         <v>158</v>
@@ -3969,11 +4779,11 @@
       <c r="A195" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B195" s="0">
-        <v>2</v>
+      <c r="B195" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="D195" s="0" t="s">
         <v>158</v>
@@ -3986,11 +4796,11 @@
       <c r="A196" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B196" s="0">
-        <v>2</v>
+      <c r="B196" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>162</v>
+        <v>373</v>
       </c>
       <c r="D196" s="0" t="s">
         <v>158</v>
@@ -4003,11 +4813,11 @@
       <c r="A197" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B197" s="0">
-        <v>3</v>
+      <c r="B197" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C197" s="0" t="s">
-        <v>162</v>
+        <v>374</v>
       </c>
       <c r="D197" s="0" t="s">
         <v>158</v>
@@ -4020,11 +4830,11 @@
       <c r="A198" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B198" s="0">
-        <v>3</v>
+      <c r="B198" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C198" s="0" t="s">
-        <v>162</v>
+        <v>374</v>
       </c>
       <c r="D198" s="0" t="s">
         <v>158</v>
@@ -4037,11 +4847,11 @@
       <c r="A199" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B199" s="0">
-        <v>3</v>
+      <c r="B199" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C199" s="0" t="s">
-        <v>162</v>
+        <v>374</v>
       </c>
       <c r="D199" s="0" t="s">
         <v>158</v>
@@ -4054,11 +4864,11 @@
       <c r="A200" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B200" s="0">
-        <v>4</v>
+      <c r="B200" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C200" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D200" s="0" t="s">
         <v>158</v>
@@ -4071,11 +4881,11 @@
       <c r="A201" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B201" s="0">
-        <v>4</v>
+      <c r="B201" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C201" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D201" s="0" t="s">
         <v>158</v>
@@ -4088,11 +4898,11 @@
       <c r="A202" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B202" s="0">
-        <v>4</v>
+      <c r="B202" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D202" s="0" t="s">
         <v>158</v>
@@ -4105,11 +4915,11 @@
       <c r="A203" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B203" s="0">
-        <v>4</v>
+      <c r="B203" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D203" s="0" t="s">
         <v>158</v>
@@ -4122,11 +4932,11 @@
       <c r="A204" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B204" s="0">
-        <v>4</v>
+      <c r="B204" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C204" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D204" s="0" t="s">
         <v>158</v>
@@ -4139,11 +4949,11 @@
       <c r="A205" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B205" s="0">
-        <v>4</v>
+      <c r="B205" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C205" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D205" s="0" t="s">
         <v>158</v>
@@ -4156,11 +4966,11 @@
       <c r="A206" s="0" t="s">
         <v>173</v>
       </c>
-      <c r="B206" s="0">
-        <v>4</v>
+      <c r="B206" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C206" s="0" t="s">
-        <v>162</v>
+        <v>375</v>
       </c>
       <c r="D206" s="0" t="s">
         <v>158</v>
@@ -4173,11 +4983,11 @@
       <c r="A207" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="B207" s="0">
-        <v>2</v>
+      <c r="B207" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C207" s="0" t="s">
-        <v>162</v>
+        <v>376</v>
       </c>
       <c r="D207" s="0" t="s">
         <v>158</v>
@@ -4190,11 +5000,11 @@
       <c r="A208" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="B208" s="0">
-        <v>2</v>
+      <c r="B208" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C208" s="0" t="s">
-        <v>162</v>
+        <v>376</v>
       </c>
       <c r="D208" s="0" t="s">
         <v>158</v>
@@ -4207,11 +5017,11 @@
       <c r="A209" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="B209" s="0">
-        <v>4</v>
+      <c r="B209" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C209" s="0" t="s">
-        <v>162</v>
+        <v>377</v>
       </c>
       <c r="D209" s="0" t="s">
         <v>158</v>
@@ -4224,11 +5034,11 @@
       <c r="A210" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="B210" s="0">
-        <v>4</v>
+      <c r="B210" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>162</v>
+        <v>377</v>
       </c>
       <c r="D210" s="0" t="s">
         <v>158</v>
@@ -4241,11 +5051,11 @@
       <c r="A211" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="B211" s="0">
-        <v>2</v>
+      <c r="B211" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>162</v>
+        <v>378</v>
       </c>
       <c r="D211" s="0" t="s">
         <v>158</v>
@@ -4258,11 +5068,11 @@
       <c r="A212" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="B212" s="0">
-        <v>4</v>
+      <c r="B212" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>162</v>
+        <v>379</v>
       </c>
       <c r="D212" s="0" t="s">
         <v>158</v>
@@ -4275,11 +5085,11 @@
       <c r="A213" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="B213" s="0">
-        <v>4</v>
+      <c r="B213" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>162</v>
+        <v>379</v>
       </c>
       <c r="D213" s="0" t="s">
         <v>158</v>
@@ -4292,11 +5102,11 @@
       <c r="A214" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="B214" s="0">
-        <v>4</v>
+      <c r="B214" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C214" s="0" t="s">
-        <v>162</v>
+        <v>379</v>
       </c>
       <c r="D214" s="0" t="s">
         <v>158</v>
@@ -4309,11 +5119,11 @@
       <c r="A215" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B215" s="0">
-        <v>1</v>
+      <c r="B215" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C215" s="0" t="s">
-        <v>162</v>
+        <v>380</v>
       </c>
       <c r="D215" s="0" t="s">
         <v>158</v>
@@ -4326,11 +5136,11 @@
       <c r="A216" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B216" s="0">
-        <v>1</v>
+      <c r="B216" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C216" s="0" t="s">
-        <v>162</v>
+        <v>380</v>
       </c>
       <c r="D216" s="0" t="s">
         <v>158</v>
@@ -4343,11 +5153,11 @@
       <c r="A217" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B217" s="0">
-        <v>1</v>
+      <c r="B217" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C217" s="0" t="s">
-        <v>162</v>
+        <v>380</v>
       </c>
       <c r="D217" s="0" t="s">
         <v>158</v>
@@ -4360,11 +5170,11 @@
       <c r="A218" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B218" s="0">
-        <v>2</v>
+      <c r="B218" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>162</v>
+        <v>381</v>
       </c>
       <c r="D218" s="0" t="s">
         <v>158</v>
@@ -4377,11 +5187,11 @@
       <c r="A219" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B219" s="0">
-        <v>4</v>
+      <c r="B219" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>162</v>
+        <v>382</v>
       </c>
       <c r="D219" s="0" t="s">
         <v>158</v>
@@ -4394,11 +5204,11 @@
       <c r="A220" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B220" s="0">
-        <v>4</v>
+      <c r="B220" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C220" s="0" t="s">
-        <v>162</v>
+        <v>382</v>
       </c>
       <c r="D220" s="0" t="s">
         <v>158</v>
@@ -4411,11 +5221,11 @@
       <c r="A221" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="B221" s="0">
-        <v>4</v>
+      <c r="B221" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C221" s="0" t="s">
-        <v>162</v>
+        <v>383</v>
       </c>
       <c r="D221" s="0" t="s">
         <v>158</v>
@@ -4428,11 +5238,11 @@
       <c r="A222" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="B222" s="0">
-        <v>4</v>
+      <c r="B222" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C222" s="0" t="s">
-        <v>162</v>
+        <v>383</v>
       </c>
       <c r="D222" s="0" t="s">
         <v>158</v>
@@ -4445,11 +5255,11 @@
       <c r="A223" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B223" s="0">
-        <v>4</v>
+      <c r="B223" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C223" s="0" t="s">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="D223" s="0" t="s">
         <v>158</v>
@@ -4462,11 +5272,11 @@
       <c r="A224" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B224" s="0">
-        <v>4</v>
+      <c r="B224" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C224" s="0" t="s">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="D224" s="0" t="s">
         <v>158</v>
@@ -4479,11 +5289,11 @@
       <c r="A225" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B225" s="0">
-        <v>4</v>
+      <c r="B225" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="D225" s="0" t="s">
         <v>158</v>
@@ -4496,11 +5306,11 @@
       <c r="A226" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B226" s="0">
-        <v>4</v>
+      <c r="B226" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="D226" s="0" t="s">
         <v>158</v>
@@ -4513,11 +5323,11 @@
       <c r="A227" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B227" s="0">
-        <v>4</v>
+      <c r="B227" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>162</v>
+        <v>384</v>
       </c>
       <c r="D227" s="0" t="s">
         <v>158</v>
@@ -4530,11 +5340,11 @@
       <c r="A228" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B228" s="0">
-        <v>2</v>
+      <c r="B228" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>162</v>
+        <v>385</v>
       </c>
       <c r="D228" s="0" t="s">
         <v>158</v>
@@ -4547,11 +5357,11 @@
       <c r="A229" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B229" s="0">
-        <v>2</v>
+      <c r="B229" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C229" s="0" t="s">
-        <v>162</v>
+        <v>385</v>
       </c>
       <c r="D229" s="0" t="s">
         <v>158</v>
@@ -4564,11 +5374,11 @@
       <c r="A230" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B230" s="0">
-        <v>2</v>
+      <c r="B230" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C230" s="0" t="s">
-        <v>162</v>
+        <v>385</v>
       </c>
       <c r="D230" s="0" t="s">
         <v>158</v>
@@ -4581,11 +5391,11 @@
       <c r="A231" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B231" s="0">
-        <v>3</v>
+      <c r="B231" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C231" s="0" t="s">
-        <v>162</v>
+        <v>386</v>
       </c>
       <c r="D231" s="0" t="s">
         <v>158</v>
@@ -4598,11 +5408,11 @@
       <c r="A232" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B232" s="0">
-        <v>4</v>
+      <c r="B232" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C232" s="0" t="s">
-        <v>162</v>
+        <v>387</v>
       </c>
       <c r="D232" s="0" t="s">
         <v>158</v>
@@ -4615,11 +5425,11 @@
       <c r="A233" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B233" s="0">
-        <v>4</v>
+      <c r="B233" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C233" s="0" t="s">
-        <v>162</v>
+        <v>387</v>
       </c>
       <c r="D233" s="0" t="s">
         <v>158</v>
@@ -4632,11 +5442,11 @@
       <c r="A234" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B234" s="0">
-        <v>4</v>
+      <c r="B234" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C234" s="0" t="s">
-        <v>162</v>
+        <v>387</v>
       </c>
       <c r="D234" s="0" t="s">
         <v>158</v>
@@ -4649,11 +5459,11 @@
       <c r="A235" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="B235" s="0">
-        <v>2</v>
+      <c r="B235" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C235" s="0" t="s">
-        <v>162</v>
+        <v>388</v>
       </c>
       <c r="D235" s="0" t="s">
         <v>158</v>
@@ -4666,11 +5476,11 @@
       <c r="A236" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="B236" s="0">
-        <v>4</v>
+      <c r="B236" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C236" s="0" t="s">
-        <v>162</v>
+        <v>389</v>
       </c>
       <c r="D236" s="0" t="s">
         <v>158</v>
@@ -4683,11 +5493,11 @@
       <c r="A237" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B237" s="0">
-        <v>3</v>
+      <c r="B237" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C237" s="0" t="s">
-        <v>162</v>
+        <v>390</v>
       </c>
       <c r="D237" s="0" t="s">
         <v>158</v>
@@ -4700,11 +5510,11 @@
       <c r="A238" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B238" s="0">
-        <v>3</v>
+      <c r="B238" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C238" s="0" t="s">
-        <v>162</v>
+        <v>390</v>
       </c>
       <c r="D238" s="0" t="s">
         <v>158</v>
@@ -4717,11 +5527,11 @@
       <c r="A239" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B239" s="0">
-        <v>3</v>
+      <c r="B239" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C239" s="0" t="s">
-        <v>162</v>
+        <v>390</v>
       </c>
       <c r="D239" s="0" t="s">
         <v>158</v>
@@ -4734,11 +5544,11 @@
       <c r="A240" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B240" s="0">
-        <v>3</v>
+      <c r="B240" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C240" s="0" t="s">
-        <v>162</v>
+        <v>390</v>
       </c>
       <c r="D240" s="0" t="s">
         <v>158</v>
@@ -4751,11 +5561,11 @@
       <c r="A241" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B241" s="0">
-        <v>3</v>
+      <c r="B241" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C241" s="0" t="s">
-        <v>162</v>
+        <v>390</v>
       </c>
       <c r="D241" s="0" t="s">
         <v>158</v>
@@ -4768,11 +5578,11 @@
       <c r="A242" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B242" s="0">
-        <v>1</v>
+      <c r="B242" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C242" s="0" t="s">
-        <v>162</v>
+        <v>391</v>
       </c>
       <c r="D242" s="0" t="s">
         <v>158</v>
@@ -4785,11 +5595,11 @@
       <c r="A243" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B243" s="0">
-        <v>1</v>
+      <c r="B243" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C243" s="0" t="s">
-        <v>162</v>
+        <v>391</v>
       </c>
       <c r="D243" s="0" t="s">
         <v>158</v>
@@ -4802,11 +5612,11 @@
       <c r="A244" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B244" s="0">
-        <v>2</v>
+      <c r="B244" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C244" s="0" t="s">
-        <v>162</v>
+        <v>392</v>
       </c>
       <c r="D244" s="0" t="s">
         <v>158</v>
@@ -4819,11 +5629,11 @@
       <c r="A245" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B245" s="0">
-        <v>3</v>
+      <c r="B245" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C245" s="0" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="D245" s="0" t="s">
         <v>158</v>
@@ -4836,11 +5646,11 @@
       <c r="A246" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B246" s="0">
-        <v>4</v>
+      <c r="B246" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C246" s="0" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D246" s="0" t="s">
         <v>158</v>
@@ -4853,11 +5663,11 @@
       <c r="A247" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B247" s="0">
-        <v>4</v>
+      <c r="B247" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C247" s="0" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D247" s="0" t="s">
         <v>158</v>
@@ -4870,11 +5680,11 @@
       <c r="A248" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B248" s="0">
-        <v>4</v>
+      <c r="B248" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C248" s="0" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D248" s="0" t="s">
         <v>158</v>
@@ -4887,11 +5697,11 @@
       <c r="A249" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B249" s="0">
-        <v>2</v>
+      <c r="B249" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C249" s="0" t="s">
-        <v>162</v>
+        <v>395</v>
       </c>
       <c r="D249" s="0" t="s">
         <v>158</v>
@@ -4904,11 +5714,11 @@
       <c r="A250" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B250" s="0">
-        <v>3</v>
+      <c r="B250" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C250" s="0" t="s">
-        <v>162</v>
+        <v>396</v>
       </c>
       <c r="D250" s="0" t="s">
         <v>158</v>
@@ -4921,11 +5731,11 @@
       <c r="A251" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B251" s="0">
-        <v>3</v>
+      <c r="B251" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C251" s="0" t="s">
-        <v>162</v>
+        <v>396</v>
       </c>
       <c r="D251" s="0" t="s">
         <v>158</v>
@@ -4938,11 +5748,11 @@
       <c r="A252" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B252" s="0">
-        <v>3</v>
+      <c r="B252" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C252" s="0" t="s">
-        <v>162</v>
+        <v>396</v>
       </c>
       <c r="D252" s="0" t="s">
         <v>158</v>
@@ -4955,11 +5765,11 @@
       <c r="A253" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B253" s="0">
-        <v>4</v>
+      <c r="B253" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C253" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D253" s="0" t="s">
         <v>158</v>
@@ -4972,11 +5782,11 @@
       <c r="A254" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B254" s="0">
-        <v>4</v>
+      <c r="B254" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C254" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D254" s="0" t="s">
         <v>158</v>
@@ -4989,11 +5799,11 @@
       <c r="A255" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B255" s="0">
-        <v>4</v>
+      <c r="B255" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C255" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D255" s="0" t="s">
         <v>158</v>
@@ -5006,11 +5816,11 @@
       <c r="A256" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B256" s="0">
-        <v>4</v>
+      <c r="B256" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C256" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D256" s="0" t="s">
         <v>158</v>
@@ -5023,11 +5833,11 @@
       <c r="A257" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B257" s="0">
-        <v>4</v>
+      <c r="B257" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C257" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D257" s="0" t="s">
         <v>158</v>
@@ -5040,11 +5850,11 @@
       <c r="A258" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B258" s="0">
-        <v>4</v>
+      <c r="B258" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C258" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D258" s="0" t="s">
         <v>158</v>
@@ -5057,11 +5867,11 @@
       <c r="A259" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B259" s="0">
-        <v>4</v>
+      <c r="B259" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C259" s="0" t="s">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="D259" s="0" t="s">
         <v>158</v>
@@ -5074,11 +5884,11 @@
       <c r="A260" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="B260" s="0">
-        <v>3</v>
+      <c r="B260" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C260" s="0" t="s">
-        <v>162</v>
+        <v>398</v>
       </c>
       <c r="D260" s="0" t="s">
         <v>158</v>
@@ -5091,11 +5901,11 @@
       <c r="A261" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="B261" s="0">
-        <v>4</v>
+      <c r="B261" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C261" s="0" t="s">
-        <v>162</v>
+        <v>399</v>
       </c>
       <c r="D261" s="0" t="s">
         <v>158</v>
@@ -5108,11 +5918,11 @@
       <c r="A262" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="B262" s="0">
-        <v>2</v>
+      <c r="B262" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C262" s="0" t="s">
-        <v>162</v>
+        <v>300</v>
       </c>
       <c r="D262" s="0" t="s">
         <v>158</v>
@@ -5125,11 +5935,11 @@
       <c r="A263" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="B263" s="0">
-        <v>3</v>
+      <c r="B263" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C263" s="0" t="s">
-        <v>162</v>
+        <v>400</v>
       </c>
       <c r="D263" s="0" t="s">
         <v>158</v>
@@ -5142,11 +5952,11 @@
       <c r="A264" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B264" s="0">
-        <v>1</v>
+      <c r="B264" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C264" s="0" t="s">
-        <v>162</v>
+        <v>401</v>
       </c>
       <c r="D264" s="0" t="s">
         <v>158</v>
@@ -5159,11 +5969,11 @@
       <c r="A265" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B265" s="0">
-        <v>1</v>
+      <c r="B265" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C265" s="0" t="s">
-        <v>162</v>
+        <v>401</v>
       </c>
       <c r="D265" s="0" t="s">
         <v>158</v>
@@ -5176,11 +5986,11 @@
       <c r="A266" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B266" s="0">
-        <v>1</v>
+      <c r="B266" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C266" s="0" t="s">
-        <v>162</v>
+        <v>401</v>
       </c>
       <c r="D266" s="0" t="s">
         <v>158</v>
@@ -5193,11 +6003,11 @@
       <c r="A267" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B267" s="0">
-        <v>2</v>
+      <c r="B267" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C267" s="0" t="s">
-        <v>162</v>
+        <v>402</v>
       </c>
       <c r="D267" s="0" t="s">
         <v>158</v>
@@ -5210,11 +6020,11 @@
       <c r="A268" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B268" s="0">
-        <v>2</v>
+      <c r="B268" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C268" s="0" t="s">
-        <v>162</v>
+        <v>402</v>
       </c>
       <c r="D268" s="0" t="s">
         <v>158</v>
@@ -5227,11 +6037,11 @@
       <c r="A269" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B269" s="0">
-        <v>4</v>
+      <c r="B269" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C269" s="0" t="s">
-        <v>162</v>
+        <v>403</v>
       </c>
       <c r="D269" s="0" t="s">
         <v>158</v>
@@ -5244,11 +6054,11 @@
       <c r="A270" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B270" s="0">
-        <v>4</v>
+      <c r="B270" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C270" s="0" t="s">
-        <v>162</v>
+        <v>403</v>
       </c>
       <c r="D270" s="0" t="s">
         <v>158</v>
@@ -5261,11 +6071,11 @@
       <c r="A271" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B271" s="0">
-        <v>4</v>
+      <c r="B271" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C271" s="0" t="s">
-        <v>162</v>
+        <v>403</v>
       </c>
       <c r="D271" s="0" t="s">
         <v>158</v>
@@ -5278,11 +6088,11 @@
       <c r="A272" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B272" s="0">
-        <v>4</v>
+      <c r="B272" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C272" s="0" t="s">
-        <v>162</v>
+        <v>403</v>
       </c>
       <c r="D272" s="0" t="s">
         <v>158</v>
@@ -5295,11 +6105,11 @@
       <c r="A273" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B273" s="0">
-        <v>4</v>
+      <c r="B273" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C273" s="0" t="s">
-        <v>162</v>
+        <v>403</v>
       </c>
       <c r="D273" s="0" t="s">
         <v>158</v>
@@ -5312,11 +6122,11 @@
       <c r="A274" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B274" s="0">
-        <v>2</v>
+      <c r="B274" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C274" s="0" t="s">
-        <v>162</v>
+        <v>404</v>
       </c>
       <c r="D274" s="0" t="s">
         <v>158</v>
@@ -5329,11 +6139,11 @@
       <c r="A275" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B275" s="0">
-        <v>2</v>
+      <c r="B275" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C275" s="0" t="s">
-        <v>162</v>
+        <v>404</v>
       </c>
       <c r="D275" s="0" t="s">
         <v>158</v>
@@ -5346,11 +6156,11 @@
       <c r="A276" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B276" s="0">
-        <v>4</v>
+      <c r="B276" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C276" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D276" s="0" t="s">
         <v>158</v>
@@ -5363,11 +6173,11 @@
       <c r="A277" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B277" s="0">
-        <v>4</v>
+      <c r="B277" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C277" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D277" s="0" t="s">
         <v>158</v>
@@ -5380,11 +6190,11 @@
       <c r="A278" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B278" s="0">
-        <v>4</v>
+      <c r="B278" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C278" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D278" s="0" t="s">
         <v>158</v>
@@ -5397,11 +6207,11 @@
       <c r="A279" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B279" s="0">
-        <v>4</v>
+      <c r="B279" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C279" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D279" s="0" t="s">
         <v>158</v>
@@ -5414,11 +6224,11 @@
       <c r="A280" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B280" s="0">
-        <v>4</v>
+      <c r="B280" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C280" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D280" s="0" t="s">
         <v>158</v>
@@ -5431,11 +6241,11 @@
       <c r="A281" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B281" s="0">
-        <v>4</v>
+      <c r="B281" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C281" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D281" s="0" t="s">
         <v>158</v>
@@ -5448,11 +6258,11 @@
       <c r="A282" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="B282" s="0">
-        <v>4</v>
+      <c r="B282" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C282" s="0" t="s">
-        <v>162</v>
+        <v>405</v>
       </c>
       <c r="D282" s="0" t="s">
         <v>158</v>
@@ -5465,11 +6275,11 @@
       <c r="A283" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B283" s="0">
-        <v>2</v>
+      <c r="B283" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C283" s="0" t="s">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="D283" s="0" t="s">
         <v>158</v>
@@ -5482,11 +6292,11 @@
       <c r="A284" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B284" s="0">
-        <v>2</v>
+      <c r="B284" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C284" s="0" t="s">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="D284" s="0" t="s">
         <v>158</v>
@@ -5499,11 +6309,11 @@
       <c r="A285" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B285" s="0">
-        <v>2</v>
+      <c r="B285" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C285" s="0" t="s">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="D285" s="0" t="s">
         <v>158</v>
@@ -5516,11 +6326,11 @@
       <c r="A286" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B286" s="0">
-        <v>2</v>
+      <c r="B286" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C286" s="0" t="s">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="D286" s="0" t="s">
         <v>158</v>
@@ -5533,11 +6343,11 @@
       <c r="A287" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B287" s="0">
-        <v>2</v>
+      <c r="B287" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C287" s="0" t="s">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="D287" s="0" t="s">
         <v>158</v>
@@ -5550,11 +6360,11 @@
       <c r="A288" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B288" s="0">
-        <v>2</v>
+      <c r="B288" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C288" s="0" t="s">
-        <v>162</v>
+        <v>406</v>
       </c>
       <c r="D288" s="0" t="s">
         <v>158</v>
@@ -5567,11 +6377,11 @@
       <c r="A289" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="B289" s="0">
-        <v>3</v>
+      <c r="B289" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C289" s="0" t="s">
-        <v>162</v>
+        <v>407</v>
       </c>
       <c r="D289" s="0" t="s">
         <v>158</v>
@@ -5584,11 +6394,11 @@
       <c r="A290" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="B290" s="0">
-        <v>2</v>
+      <c r="B290" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C290" s="0" t="s">
-        <v>162</v>
+        <v>408</v>
       </c>
       <c r="D290" s="0" t="s">
         <v>158</v>
@@ -5601,11 +6411,11 @@
       <c r="A291" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="B291" s="0">
-        <v>2</v>
+      <c r="B291" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C291" s="0" t="s">
-        <v>162</v>
+        <v>408</v>
       </c>
       <c r="D291" s="0" t="s">
         <v>158</v>
@@ -5618,11 +6428,11 @@
       <c r="A292" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B292" s="0">
-        <v>1</v>
+      <c r="B292" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C292" s="0" t="s">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="D292" s="0" t="s">
         <v>158</v>
@@ -5635,11 +6445,11 @@
       <c r="A293" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B293" s="0">
-        <v>1</v>
+      <c r="B293" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C293" s="0" t="s">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="D293" s="0" t="s">
         <v>158</v>
@@ -5652,11 +6462,11 @@
       <c r="A294" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B294" s="0">
-        <v>1</v>
+      <c r="B294" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C294" s="0" t="s">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="D294" s="0" t="s">
         <v>158</v>
@@ -5669,11 +6479,11 @@
       <c r="A295" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B295" s="0">
-        <v>1</v>
+      <c r="B295" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C295" s="0" t="s">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="D295" s="0" t="s">
         <v>158</v>
@@ -5686,11 +6496,11 @@
       <c r="A296" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B296" s="0">
-        <v>1</v>
+      <c r="B296" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C296" s="0" t="s">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="D296" s="0" t="s">
         <v>158</v>
@@ -5703,11 +6513,11 @@
       <c r="A297" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B297" s="0">
-        <v>1</v>
+      <c r="B297" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C297" s="0" t="s">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="D297" s="0" t="s">
         <v>158</v>
@@ -5720,11 +6530,11 @@
       <c r="A298" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B298" s="0">
-        <v>2</v>
+      <c r="B298" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C298" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D298" s="0" t="s">
         <v>158</v>
@@ -5737,11 +6547,11 @@
       <c r="A299" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B299" s="0">
-        <v>2</v>
+      <c r="B299" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C299" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D299" s="0" t="s">
         <v>158</v>
@@ -5754,11 +6564,11 @@
       <c r="A300" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B300" s="0">
-        <v>2</v>
+      <c r="B300" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C300" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D300" s="0" t="s">
         <v>158</v>
@@ -5771,11 +6581,11 @@
       <c r="A301" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B301" s="0">
-        <v>2</v>
+      <c r="B301" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C301" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D301" s="0" t="s">
         <v>158</v>
@@ -5788,11 +6598,11 @@
       <c r="A302" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B302" s="0">
-        <v>2</v>
+      <c r="B302" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C302" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D302" s="0" t="s">
         <v>158</v>
@@ -5805,11 +6615,11 @@
       <c r="A303" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B303" s="0">
-        <v>2</v>
+      <c r="B303" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C303" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D303" s="0" t="s">
         <v>158</v>
@@ -5822,11 +6632,11 @@
       <c r="A304" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B304" s="0">
-        <v>2</v>
+      <c r="B304" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C304" s="0" t="s">
-        <v>162</v>
+        <v>410</v>
       </c>
       <c r="D304" s="0" t="s">
         <v>158</v>
@@ -5839,11 +6649,11 @@
       <c r="A305" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B305" s="0">
-        <v>3</v>
+      <c r="B305" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C305" s="0" t="s">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="D305" s="0" t="s">
         <v>158</v>
@@ -5856,11 +6666,11 @@
       <c r="A306" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B306" s="0">
-        <v>3</v>
+      <c r="B306" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C306" s="0" t="s">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="D306" s="0" t="s">
         <v>158</v>
@@ -5873,11 +6683,11 @@
       <c r="A307" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B307" s="0">
-        <v>3</v>
+      <c r="B307" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C307" s="0" t="s">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="D307" s="0" t="s">
         <v>158</v>
@@ -5890,11 +6700,11 @@
       <c r="A308" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B308" s="0">
-        <v>3</v>
+      <c r="B308" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C308" s="0" t="s">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="D308" s="0" t="s">
         <v>158</v>
@@ -5907,11 +6717,11 @@
       <c r="A309" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B309" s="0">
-        <v>3</v>
+      <c r="B309" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C309" s="0" t="s">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="D309" s="0" t="s">
         <v>158</v>
@@ -5924,11 +6734,11 @@
       <c r="A310" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B310" s="0">
-        <v>4</v>
+      <c r="B310" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C310" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D310" s="0" t="s">
         <v>158</v>
@@ -5941,11 +6751,11 @@
       <c r="A311" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B311" s="0">
-        <v>4</v>
+      <c r="B311" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C311" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D311" s="0" t="s">
         <v>158</v>
@@ -5958,11 +6768,11 @@
       <c r="A312" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B312" s="0">
-        <v>4</v>
+      <c r="B312" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C312" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D312" s="0" t="s">
         <v>158</v>
@@ -5975,11 +6785,11 @@
       <c r="A313" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B313" s="0">
-        <v>4</v>
+      <c r="B313" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C313" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D313" s="0" t="s">
         <v>158</v>
@@ -5992,11 +6802,11 @@
       <c r="A314" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B314" s="0">
-        <v>4</v>
+      <c r="B314" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C314" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D314" s="0" t="s">
         <v>158</v>
@@ -6009,11 +6819,11 @@
       <c r="A315" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B315" s="0">
-        <v>4</v>
+      <c r="B315" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C315" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D315" s="0" t="s">
         <v>158</v>
@@ -6026,11 +6836,11 @@
       <c r="A316" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B316" s="0">
-        <v>4</v>
+      <c r="B316" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C316" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D316" s="0" t="s">
         <v>158</v>
@@ -6043,11 +6853,11 @@
       <c r="A317" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B317" s="0">
-        <v>4</v>
+      <c r="B317" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C317" s="0" t="s">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="D317" s="0" t="s">
         <v>158</v>
@@ -6060,11 +6870,11 @@
       <c r="A318" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="B318" s="0">
-        <v>1</v>
+      <c r="B318" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C318" s="0" t="s">
-        <v>162</v>
+        <v>413</v>
       </c>
       <c r="D318" s="0" t="s">
         <v>158</v>
@@ -6077,11 +6887,11 @@
       <c r="A319" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="B319" s="0">
-        <v>2</v>
+      <c r="B319" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C319" s="0" t="s">
-        <v>162</v>
+        <v>414</v>
       </c>
       <c r="D319" s="0" t="s">
         <v>158</v>
@@ -6094,11 +6904,11 @@
       <c r="A320" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B320" s="0">
-        <v>1</v>
+      <c r="B320" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C320" s="0" t="s">
-        <v>162</v>
+        <v>415</v>
       </c>
       <c r="D320" s="0" t="s">
         <v>158</v>
@@ -6111,11 +6921,11 @@
       <c r="A321" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B321" s="0">
-        <v>1</v>
+      <c r="B321" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C321" s="0" t="s">
-        <v>162</v>
+        <v>415</v>
       </c>
       <c r="D321" s="0" t="s">
         <v>158</v>
@@ -6128,11 +6938,11 @@
       <c r="A322" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B322" s="0">
-        <v>1</v>
+      <c r="B322" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C322" s="0" t="s">
-        <v>162</v>
+        <v>415</v>
       </c>
       <c r="D322" s="0" t="s">
         <v>158</v>
@@ -6145,11 +6955,11 @@
       <c r="A323" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B323" s="0">
-        <v>1</v>
+      <c r="B323" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C323" s="0" t="s">
-        <v>162</v>
+        <v>415</v>
       </c>
       <c r="D323" s="0" t="s">
         <v>158</v>
@@ -6162,11 +6972,11 @@
       <c r="A324" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B324" s="0">
-        <v>1</v>
+      <c r="B324" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C324" s="0" t="s">
-        <v>162</v>
+        <v>415</v>
       </c>
       <c r="D324" s="0" t="s">
         <v>158</v>
@@ -6179,11 +6989,11 @@
       <c r="A325" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B325" s="0">
-        <v>2</v>
+      <c r="B325" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C325" s="0" t="s">
-        <v>162</v>
+        <v>416</v>
       </c>
       <c r="D325" s="0" t="s">
         <v>158</v>
@@ -6196,11 +7006,11 @@
       <c r="A326" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B326" s="0">
-        <v>2</v>
+      <c r="B326" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C326" s="0" t="s">
-        <v>162</v>
+        <v>416</v>
       </c>
       <c r="D326" s="0" t="s">
         <v>158</v>
@@ -6213,11 +7023,11 @@
       <c r="A327" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B327" s="0">
-        <v>2</v>
+      <c r="B327" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C327" s="0" t="s">
-        <v>162</v>
+        <v>416</v>
       </c>
       <c r="D327" s="0" t="s">
         <v>158</v>
@@ -6230,11 +7040,11 @@
       <c r="A328" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B328" s="0">
-        <v>2</v>
+      <c r="B328" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C328" s="0" t="s">
-        <v>162</v>
+        <v>416</v>
       </c>
       <c r="D328" s="0" t="s">
         <v>158</v>
@@ -6247,11 +7057,11 @@
       <c r="A329" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B329" s="0">
-        <v>2</v>
+      <c r="B329" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C329" s="0" t="s">
-        <v>162</v>
+        <v>416</v>
       </c>
       <c r="D329" s="0" t="s">
         <v>158</v>
@@ -6264,11 +7074,11 @@
       <c r="A330" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B330" s="0">
-        <v>4</v>
+      <c r="B330" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C330" s="0" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="D330" s="0" t="s">
         <v>158</v>
@@ -6281,11 +7091,11 @@
       <c r="A331" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B331" s="0">
-        <v>4</v>
+      <c r="B331" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C331" s="0" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="D331" s="0" t="s">
         <v>158</v>
@@ -6298,11 +7108,11 @@
       <c r="A332" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B332" s="0">
-        <v>4</v>
+      <c r="B332" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C332" s="0" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="D332" s="0" t="s">
         <v>158</v>
@@ -6315,11 +7125,11 @@
       <c r="A333" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B333" s="0">
-        <v>4</v>
+      <c r="B333" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C333" s="0" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="D333" s="0" t="s">
         <v>158</v>
@@ -6332,11 +7142,11 @@
       <c r="A334" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B334" s="0">
-        <v>4</v>
+      <c r="B334" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C334" s="0" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="D334" s="0" t="s">
         <v>158</v>
@@ -6349,11 +7159,11 @@
       <c r="A335" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="B335" s="0">
-        <v>4</v>
+      <c r="B335" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C335" s="0" t="s">
-        <v>162</v>
+        <v>417</v>
       </c>
       <c r="D335" s="0" t="s">
         <v>158</v>
@@ -6366,11 +7176,11 @@
       <c r="A336" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B336" s="0">
-        <v>1</v>
+      <c r="B336" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C336" s="0" t="s">
-        <v>162</v>
+        <v>418</v>
       </c>
       <c r="D336" s="0" t="s">
         <v>158</v>
@@ -6383,11 +7193,11 @@
       <c r="A337" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B337" s="0">
-        <v>3</v>
+      <c r="B337" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C337" s="0" t="s">
-        <v>162</v>
+        <v>419</v>
       </c>
       <c r="D337" s="0" t="s">
         <v>158</v>
@@ -6400,11 +7210,11 @@
       <c r="A338" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B338" s="0">
-        <v>4</v>
+      <c r="B338" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C338" s="0" t="s">
-        <v>162</v>
+        <v>420</v>
       </c>
       <c r="D338" s="0" t="s">
         <v>158</v>
@@ -6417,11 +7227,11 @@
       <c r="A339" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B339" s="0">
-        <v>4</v>
+      <c r="B339" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C339" s="0" t="s">
-        <v>162</v>
+        <v>420</v>
       </c>
       <c r="D339" s="0" t="s">
         <v>158</v>
@@ -6434,11 +7244,11 @@
       <c r="A340" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="B340" s="0">
-        <v>4</v>
+      <c r="B340" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C340" s="0" t="s">
-        <v>162</v>
+        <v>420</v>
       </c>
       <c r="D340" s="0" t="s">
         <v>158</v>
@@ -6451,11 +7261,11 @@
       <c r="A341" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B341" s="0">
-        <v>1</v>
+      <c r="B341" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C341" s="0" t="s">
-        <v>162</v>
+        <v>421</v>
       </c>
       <c r="D341" s="0" t="s">
         <v>158</v>
@@ -6468,11 +7278,11 @@
       <c r="A342" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B342" s="0">
-        <v>1</v>
+      <c r="B342" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C342" s="0" t="s">
-        <v>162</v>
+        <v>421</v>
       </c>
       <c r="D342" s="0" t="s">
         <v>158</v>
@@ -6485,11 +7295,11 @@
       <c r="A343" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B343" s="0">
-        <v>1</v>
+      <c r="B343" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C343" s="0" t="s">
-        <v>162</v>
+        <v>421</v>
       </c>
       <c r="D343" s="0" t="s">
         <v>158</v>
@@ -6502,11 +7312,11 @@
       <c r="A344" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B344" s="0">
-        <v>1</v>
+      <c r="B344" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C344" s="0" t="s">
-        <v>162</v>
+        <v>421</v>
       </c>
       <c r="D344" s="0" t="s">
         <v>158</v>
@@ -6519,11 +7329,11 @@
       <c r="A345" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B345" s="0">
-        <v>3</v>
+      <c r="B345" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C345" s="0" t="s">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="D345" s="0" t="s">
         <v>158</v>
@@ -6536,11 +7346,11 @@
       <c r="A346" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B346" s="0">
-        <v>3</v>
+      <c r="B346" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C346" s="0" t="s">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="D346" s="0" t="s">
         <v>158</v>
@@ -6553,11 +7363,11 @@
       <c r="A347" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B347" s="0">
-        <v>3</v>
+      <c r="B347" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C347" s="0" t="s">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="D347" s="0" t="s">
         <v>158</v>
@@ -6570,11 +7380,11 @@
       <c r="A348" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B348" s="0">
-        <v>4</v>
+      <c r="B348" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C348" s="0" t="s">
-        <v>162</v>
+        <v>423</v>
       </c>
       <c r="D348" s="0" t="s">
         <v>158</v>
@@ -6587,11 +7397,11 @@
       <c r="A349" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B349" s="0">
-        <v>1</v>
+      <c r="B349" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C349" s="0" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="D349" s="0" t="s">
         <v>158</v>
@@ -6604,11 +7414,11 @@
       <c r="A350" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B350" s="0">
-        <v>1</v>
+      <c r="B350" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C350" s="0" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="D350" s="0" t="s">
         <v>158</v>
@@ -6621,11 +7431,11 @@
       <c r="A351" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B351" s="0">
-        <v>1</v>
+      <c r="B351" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C351" s="0" t="s">
-        <v>162</v>
+        <v>309</v>
       </c>
       <c r="D351" s="0" t="s">
         <v>158</v>
@@ -6638,11 +7448,11 @@
       <c r="A352" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B352" s="0">
-        <v>2</v>
+      <c r="B352" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C352" s="0" t="s">
-        <v>162</v>
+        <v>310</v>
       </c>
       <c r="D352" s="0" t="s">
         <v>158</v>
@@ -6655,11 +7465,11 @@
       <c r="A353" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B353" s="0">
-        <v>3</v>
+      <c r="B353" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C353" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D353" s="0" t="s">
         <v>158</v>
@@ -6672,11 +7482,11 @@
       <c r="A354" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B354" s="0">
-        <v>3</v>
+      <c r="B354" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C354" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D354" s="0" t="s">
         <v>158</v>
@@ -6689,11 +7499,11 @@
       <c r="A355" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B355" s="0">
-        <v>3</v>
+      <c r="B355" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C355" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D355" s="0" t="s">
         <v>158</v>
@@ -6706,11 +7516,11 @@
       <c r="A356" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B356" s="0">
-        <v>3</v>
+      <c r="B356" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C356" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D356" s="0" t="s">
         <v>158</v>
@@ -6723,11 +7533,11 @@
       <c r="A357" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B357" s="0">
-        <v>3</v>
+      <c r="B357" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C357" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D357" s="0" t="s">
         <v>158</v>
@@ -6740,11 +7550,11 @@
       <c r="A358" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B358" s="0">
-        <v>3</v>
+      <c r="B358" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C358" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D358" s="0" t="s">
         <v>158</v>
@@ -6757,11 +7567,11 @@
       <c r="A359" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B359" s="0">
-        <v>3</v>
+      <c r="B359" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C359" s="0" t="s">
-        <v>162</v>
+        <v>424</v>
       </c>
       <c r="D359" s="0" t="s">
         <v>158</v>
@@ -6774,11 +7584,11 @@
       <c r="A360" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B360" s="0">
-        <v>4</v>
+      <c r="B360" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C360" s="0" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="D360" s="0" t="s">
         <v>158</v>
@@ -6791,11 +7601,11 @@
       <c r="A361" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B361" s="0">
-        <v>4</v>
+      <c r="B361" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C361" s="0" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="D361" s="0" t="s">
         <v>158</v>
@@ -6808,11 +7618,11 @@
       <c r="A362" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B362" s="0">
-        <v>4</v>
+      <c r="B362" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C362" s="0" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="D362" s="0" t="s">
         <v>158</v>
@@ -6825,11 +7635,11 @@
       <c r="A363" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B363" s="0">
-        <v>4</v>
+      <c r="B363" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C363" s="0" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="D363" s="0" t="s">
         <v>158</v>
@@ -6842,11 +7652,11 @@
       <c r="A364" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="B364" s="0">
-        <v>4</v>
+      <c r="B364" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C364" s="0" t="s">
-        <v>162</v>
+        <v>425</v>
       </c>
       <c r="D364" s="0" t="s">
         <v>158</v>
@@ -6859,11 +7669,11 @@
       <c r="A365" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B365" s="0">
-        <v>1</v>
+      <c r="B365" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C365" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D365" s="0" t="s">
         <v>158</v>
@@ -6876,11 +7686,11 @@
       <c r="A366" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B366" s="0">
-        <v>1</v>
+      <c r="B366" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C366" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D366" s="0" t="s">
         <v>158</v>
@@ -6893,11 +7703,11 @@
       <c r="A367" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B367" s="0">
-        <v>1</v>
+      <c r="B367" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C367" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D367" s="0" t="s">
         <v>158</v>
@@ -6910,11 +7720,11 @@
       <c r="A368" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B368" s="0">
-        <v>1</v>
+      <c r="B368" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C368" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D368" s="0" t="s">
         <v>158</v>
@@ -6927,11 +7737,11 @@
       <c r="A369" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B369" s="0">
-        <v>1</v>
+      <c r="B369" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C369" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D369" s="0" t="s">
         <v>158</v>
@@ -6944,11 +7754,11 @@
       <c r="A370" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B370" s="0">
-        <v>1</v>
+      <c r="B370" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C370" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D370" s="0" t="s">
         <v>158</v>
@@ -6961,11 +7771,11 @@
       <c r="A371" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B371" s="0">
-        <v>1</v>
+      <c r="B371" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C371" s="0" t="s">
-        <v>162</v>
+        <v>426</v>
       </c>
       <c r="D371" s="0" t="s">
         <v>158</v>
@@ -6978,11 +7788,11 @@
       <c r="A372" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B372" s="0">
-        <v>2</v>
+      <c r="B372" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C372" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D372" s="0" t="s">
         <v>158</v>
@@ -6995,11 +7805,11 @@
       <c r="A373" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B373" s="0">
-        <v>2</v>
+      <c r="B373" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C373" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D373" s="0" t="s">
         <v>158</v>
@@ -7012,11 +7822,11 @@
       <c r="A374" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B374" s="0">
-        <v>2</v>
+      <c r="B374" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C374" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D374" s="0" t="s">
         <v>158</v>
@@ -7029,11 +7839,11 @@
       <c r="A375" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B375" s="0">
-        <v>2</v>
+      <c r="B375" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C375" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D375" s="0" t="s">
         <v>158</v>
@@ -7046,11 +7856,11 @@
       <c r="A376" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B376" s="0">
-        <v>2</v>
+      <c r="B376" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C376" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D376" s="0" t="s">
         <v>158</v>
@@ -7063,11 +7873,11 @@
       <c r="A377" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B377" s="0">
-        <v>2</v>
+      <c r="B377" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C377" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D377" s="0" t="s">
         <v>158</v>
@@ -7080,11 +7890,11 @@
       <c r="A378" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B378" s="0">
-        <v>2</v>
+      <c r="B378" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C378" s="0" t="s">
-        <v>162</v>
+        <v>427</v>
       </c>
       <c r="D378" s="0" t="s">
         <v>158</v>
@@ -7097,11 +7907,11 @@
       <c r="A379" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B379" s="0">
-        <v>3</v>
+      <c r="B379" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C379" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D379" s="0" t="s">
         <v>158</v>
@@ -7114,11 +7924,11 @@
       <c r="A380" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B380" s="0">
-        <v>3</v>
+      <c r="B380" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C380" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D380" s="0" t="s">
         <v>158</v>
@@ -7131,11 +7941,11 @@
       <c r="A381" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B381" s="0">
-        <v>3</v>
+      <c r="B381" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C381" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D381" s="0" t="s">
         <v>158</v>
@@ -7148,11 +7958,11 @@
       <c r="A382" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B382" s="0">
-        <v>3</v>
+      <c r="B382" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C382" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D382" s="0" t="s">
         <v>158</v>
@@ -7165,11 +7975,11 @@
       <c r="A383" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B383" s="0">
-        <v>3</v>
+      <c r="B383" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C383" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D383" s="0" t="s">
         <v>158</v>
@@ -7182,11 +7992,11 @@
       <c r="A384" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B384" s="0">
-        <v>3</v>
+      <c r="B384" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C384" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D384" s="0" t="s">
         <v>158</v>
@@ -7199,11 +8009,11 @@
       <c r="A385" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B385" s="0">
-        <v>3</v>
+      <c r="B385" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C385" s="0" t="s">
-        <v>162</v>
+        <v>428</v>
       </c>
       <c r="D385" s="0" t="s">
         <v>158</v>
@@ -7216,11 +8026,11 @@
       <c r="A386" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="B386" s="0">
-        <v>4</v>
+      <c r="B386" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C386" s="0" t="s">
-        <v>162</v>
+        <v>429</v>
       </c>
       <c r="D386" s="0" t="s">
         <v>158</v>
@@ -7233,11 +8043,11 @@
       <c r="A387" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B387" s="0">
-        <v>1</v>
+      <c r="B387" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C387" s="0" t="s">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="D387" s="0" t="s">
         <v>158</v>
@@ -7250,11 +8060,11 @@
       <c r="A388" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B388" s="0">
-        <v>1</v>
+      <c r="B388" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C388" s="0" t="s">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="D388" s="0" t="s">
         <v>158</v>
@@ -7267,11 +8077,11 @@
       <c r="A389" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B389" s="0">
-        <v>1</v>
+      <c r="B389" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C389" s="0" t="s">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="D389" s="0" t="s">
         <v>158</v>
@@ -7284,11 +8094,11 @@
       <c r="A390" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B390" s="0">
-        <v>1</v>
+      <c r="B390" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C390" s="0" t="s">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="D390" s="0" t="s">
         <v>158</v>
@@ -7301,11 +8111,11 @@
       <c r="A391" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B391" s="0">
-        <v>3</v>
+      <c r="B391" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C391" s="0" t="s">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="D391" s="0" t="s">
         <v>158</v>
@@ -7318,11 +8128,11 @@
       <c r="A392" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B392" s="0">
-        <v>3</v>
+      <c r="B392" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C392" s="0" t="s">
-        <v>162</v>
+        <v>431</v>
       </c>
       <c r="D392" s="0" t="s">
         <v>158</v>
@@ -7335,11 +8145,11 @@
       <c r="A393" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="B393" s="0">
-        <v>4</v>
+      <c r="B393" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C393" s="0" t="s">
-        <v>162</v>
+        <v>432</v>
       </c>
       <c r="D393" s="0" t="s">
         <v>158</v>
@@ -7352,11 +8162,11 @@
       <c r="A394" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B394" s="0">
-        <v>3</v>
+      <c r="B394" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C394" s="0" t="s">
-        <v>162</v>
+        <v>433</v>
       </c>
       <c r="D394" s="0" t="s">
         <v>158</v>
@@ -7369,11 +8179,11 @@
       <c r="A395" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B395" s="0">
-        <v>4</v>
+      <c r="B395" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C395" s="0" t="s">
-        <v>162</v>
+        <v>434</v>
       </c>
       <c r="D395" s="0" t="s">
         <v>158</v>
@@ -7386,11 +8196,11 @@
       <c r="A396" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="B396" s="0">
-        <v>4</v>
+      <c r="B396" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C396" s="0" t="s">
-        <v>162</v>
+        <v>434</v>
       </c>
       <c r="D396" s="0" t="s">
         <v>158</v>
@@ -7403,11 +8213,11 @@
       <c r="A397" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B397" s="0">
-        <v>2</v>
+      <c r="B397" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C397" s="0" t="s">
-        <v>162</v>
+        <v>435</v>
       </c>
       <c r="D397" s="0" t="s">
         <v>158</v>
@@ -7420,11 +8230,11 @@
       <c r="A398" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B398" s="0">
-        <v>2</v>
+      <c r="B398" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C398" s="0" t="s">
-        <v>162</v>
+        <v>435</v>
       </c>
       <c r="D398" s="0" t="s">
         <v>158</v>
@@ -7437,11 +8247,11 @@
       <c r="A399" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="B399" s="0">
-        <v>2</v>
+      <c r="B399" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C399" s="0" t="s">
-        <v>162</v>
+        <v>435</v>
       </c>
       <c r="D399" s="0" t="s">
         <v>158</v>
@@ -7454,11 +8264,11 @@
       <c r="A400" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B400" s="0">
-        <v>1</v>
+      <c r="B400" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C400" s="0" t="s">
-        <v>162</v>
+        <v>436</v>
       </c>
       <c r="D400" s="0" t="s">
         <v>158</v>
@@ -7471,11 +8281,11 @@
       <c r="A401" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B401" s="0">
-        <v>1</v>
+      <c r="B401" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C401" s="0" t="s">
-        <v>162</v>
+        <v>436</v>
       </c>
       <c r="D401" s="0" t="s">
         <v>158</v>
@@ -7488,11 +8298,11 @@
       <c r="A402" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B402" s="0">
-        <v>1</v>
+      <c r="B402" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C402" s="0" t="s">
-        <v>162</v>
+        <v>436</v>
       </c>
       <c r="D402" s="0" t="s">
         <v>158</v>
@@ -7505,11 +8315,11 @@
       <c r="A403" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B403" s="0">
-        <v>3</v>
+      <c r="B403" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C403" s="0" t="s">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="D403" s="0" t="s">
         <v>158</v>
@@ -7522,11 +8332,11 @@
       <c r="A404" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B404" s="0">
-        <v>3</v>
+      <c r="B404" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C404" s="0" t="s">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="D404" s="0" t="s">
         <v>158</v>
@@ -7539,11 +8349,11 @@
       <c r="A405" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B405" s="0">
-        <v>3</v>
+      <c r="B405" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C405" s="0" t="s">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="D405" s="0" t="s">
         <v>158</v>
@@ -7556,11 +8366,11 @@
       <c r="A406" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B406" s="0">
-        <v>3</v>
+      <c r="B406" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C406" s="0" t="s">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="D406" s="0" t="s">
         <v>158</v>
@@ -7573,11 +8383,11 @@
       <c r="A407" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B407" s="0">
-        <v>3</v>
+      <c r="B407" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C407" s="0" t="s">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="D407" s="0" t="s">
         <v>158</v>
@@ -7590,11 +8400,11 @@
       <c r="A408" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="B408" s="0">
-        <v>3</v>
+      <c r="B408" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C408" s="0" t="s">
-        <v>162</v>
+        <v>437</v>
       </c>
       <c r="D408" s="0" t="s">
         <v>158</v>
@@ -7607,11 +8417,11 @@
       <c r="A409" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B409" s="0">
-        <v>2</v>
+      <c r="B409" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C409" s="0" t="s">
-        <v>162</v>
+        <v>438</v>
       </c>
       <c r="D409" s="0" t="s">
         <v>158</v>
@@ -7624,11 +8434,11 @@
       <c r="A410" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="B410" s="0">
-        <v>3</v>
+      <c r="B410" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C410" s="0" t="s">
-        <v>162</v>
+        <v>439</v>
       </c>
       <c r="D410" s="0" t="s">
         <v>158</v>
@@ -7641,11 +8451,11 @@
       <c r="A411" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B411" s="0">
-        <v>3</v>
+      <c r="B411" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C411" s="0" t="s">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="D411" s="0" t="s">
         <v>158</v>
@@ -7658,11 +8468,11 @@
       <c r="A412" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B412" s="0">
-        <v>3</v>
+      <c r="B412" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C412" s="0" t="s">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="D412" s="0" t="s">
         <v>158</v>
@@ -7675,11 +8485,11 @@
       <c r="A413" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B413" s="0">
-        <v>3</v>
+      <c r="B413" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C413" s="0" t="s">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="D413" s="0" t="s">
         <v>158</v>
@@ -7692,11 +8502,11 @@
       <c r="A414" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B414" s="0">
-        <v>3</v>
+      <c r="B414" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C414" s="0" t="s">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="D414" s="0" t="s">
         <v>158</v>
@@ -7709,11 +8519,11 @@
       <c r="A415" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B415" s="0">
-        <v>3</v>
+      <c r="B415" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C415" s="0" t="s">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="D415" s="0" t="s">
         <v>158</v>
@@ -7726,11 +8536,11 @@
       <c r="A416" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B416" s="0">
-        <v>3</v>
+      <c r="B416" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C416" s="0" t="s">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="D416" s="0" t="s">
         <v>158</v>
@@ -7743,11 +8553,11 @@
       <c r="A417" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="B417" s="0">
-        <v>4</v>
+      <c r="B417" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C417" s="0" t="s">
-        <v>162</v>
+        <v>441</v>
       </c>
       <c r="D417" s="0" t="s">
         <v>158</v>
@@ -7760,11 +8570,11 @@
       <c r="A418" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B418" s="0">
-        <v>4</v>
+      <c r="B418" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C418" s="0" t="s">
-        <v>162</v>
+        <v>442</v>
       </c>
       <c r="D418" s="0" t="s">
         <v>158</v>
@@ -7777,11 +8587,11 @@
       <c r="A419" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="B419" s="0">
-        <v>4</v>
+      <c r="B419" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C419" s="0" t="s">
-        <v>162</v>
+        <v>442</v>
       </c>
       <c r="D419" s="0" t="s">
         <v>158</v>
@@ -7794,11 +8604,11 @@
       <c r="A420" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B420" s="0">
-        <v>1</v>
+      <c r="B420" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C420" s="0" t="s">
-        <v>162</v>
+        <v>443</v>
       </c>
       <c r="D420" s="0" t="s">
         <v>158</v>
@@ -7811,11 +8621,11 @@
       <c r="A421" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B421" s="0">
-        <v>2</v>
+      <c r="B421" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C421" s="0" t="s">
-        <v>162</v>
+        <v>444</v>
       </c>
       <c r="D421" s="0" t="s">
         <v>158</v>
@@ -7828,11 +8638,11 @@
       <c r="A422" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B422" s="0">
-        <v>2</v>
+      <c r="B422" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C422" s="0" t="s">
-        <v>162</v>
+        <v>444</v>
       </c>
       <c r="D422" s="0" t="s">
         <v>158</v>
@@ -7845,11 +8655,11 @@
       <c r="A423" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B423" s="0">
-        <v>3</v>
+      <c r="B423" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C423" s="0" t="s">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="D423" s="0" t="s">
         <v>158</v>
@@ -7862,11 +8672,11 @@
       <c r="A424" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B424" s="0">
-        <v>3</v>
+      <c r="B424" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C424" s="0" t="s">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="D424" s="0" t="s">
         <v>158</v>
@@ -7879,11 +8689,11 @@
       <c r="A425" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B425" s="0">
-        <v>3</v>
+      <c r="B425" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C425" s="0" t="s">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="D425" s="0" t="s">
         <v>158</v>
@@ -7896,11 +8706,11 @@
       <c r="A426" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B426" s="0">
-        <v>3</v>
+      <c r="B426" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C426" s="0" t="s">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="D426" s="0" t="s">
         <v>158</v>
@@ -7913,11 +8723,11 @@
       <c r="A427" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="B427" s="0">
-        <v>3</v>
+      <c r="B427" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C427" s="0" t="s">
-        <v>162</v>
+        <v>445</v>
       </c>
       <c r="D427" s="0" t="s">
         <v>158</v>
@@ -7930,11 +8740,11 @@
       <c r="A428" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B428" s="0">
-        <v>1</v>
+      <c r="B428" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C428" s="0" t="s">
-        <v>162</v>
+        <v>446</v>
       </c>
       <c r="D428" s="0" t="s">
         <v>158</v>
@@ -7947,11 +8757,11 @@
       <c r="A429" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B429" s="0">
-        <v>2</v>
+      <c r="B429" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C429" s="0" t="s">
-        <v>162</v>
+        <v>447</v>
       </c>
       <c r="D429" s="0" t="s">
         <v>158</v>
@@ -7964,11 +8774,11 @@
       <c r="A430" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="B430" s="0">
-        <v>2</v>
+      <c r="B430" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C430" s="0" t="s">
-        <v>162</v>
+        <v>447</v>
       </c>
       <c r="D430" s="0" t="s">
         <v>158</v>
@@ -7981,11 +8791,11 @@
       <c r="A431" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B431" s="0">
-        <v>1</v>
+      <c r="B431" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C431" s="0" t="s">
-        <v>162</v>
+        <v>448</v>
       </c>
       <c r="D431" s="0" t="s">
         <v>158</v>
@@ -7998,11 +8808,11 @@
       <c r="A432" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B432" s="0">
-        <v>2</v>
+      <c r="B432" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C432" s="0" t="s">
-        <v>162</v>
+        <v>449</v>
       </c>
       <c r="D432" s="0" t="s">
         <v>158</v>
@@ -8015,11 +8825,11 @@
       <c r="A433" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B433" s="0">
-        <v>2</v>
+      <c r="B433" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C433" s="0" t="s">
-        <v>162</v>
+        <v>449</v>
       </c>
       <c r="D433" s="0" t="s">
         <v>158</v>
@@ -8032,11 +8842,11 @@
       <c r="A434" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B434" s="0">
-        <v>2</v>
+      <c r="B434" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C434" s="0" t="s">
-        <v>162</v>
+        <v>449</v>
       </c>
       <c r="D434" s="0" t="s">
         <v>158</v>
@@ -8049,11 +8859,11 @@
       <c r="A435" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B435" s="0">
-        <v>3</v>
+      <c r="B435" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C435" s="0" t="s">
-        <v>162</v>
+        <v>450</v>
       </c>
       <c r="D435" s="0" t="s">
         <v>158</v>
@@ -8066,11 +8876,11 @@
       <c r="A436" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B436" s="0">
-        <v>4</v>
+      <c r="B436" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C436" s="0" t="s">
-        <v>162</v>
+        <v>451</v>
       </c>
       <c r="D436" s="0" t="s">
         <v>158</v>
@@ -8083,11 +8893,11 @@
       <c r="A437" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="B437" s="0">
-        <v>4</v>
+      <c r="B437" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C437" s="0" t="s">
-        <v>162</v>
+        <v>451</v>
       </c>
       <c r="D437" s="0" t="s">
         <v>158</v>
@@ -8100,11 +8910,11 @@
       <c r="A438" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B438" s="0">
-        <v>1</v>
+      <c r="B438" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C438" s="0" t="s">
-        <v>162</v>
+        <v>452</v>
       </c>
       <c r="D438" s="0" t="s">
         <v>158</v>
@@ -8117,11 +8927,11 @@
       <c r="A439" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B439" s="0">
-        <v>1</v>
+      <c r="B439" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C439" s="0" t="s">
-        <v>162</v>
+        <v>452</v>
       </c>
       <c r="D439" s="0" t="s">
         <v>158</v>
@@ -8134,11 +8944,11 @@
       <c r="A440" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B440" s="0">
-        <v>2</v>
+      <c r="B440" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C440" s="0" t="s">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="D440" s="0" t="s">
         <v>158</v>
@@ -8151,11 +8961,11 @@
       <c r="A441" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B441" s="0">
-        <v>2</v>
+      <c r="B441" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C441" s="0" t="s">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="D441" s="0" t="s">
         <v>158</v>
@@ -8168,11 +8978,11 @@
       <c r="A442" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B442" s="0">
-        <v>2</v>
+      <c r="B442" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C442" s="0" t="s">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="D442" s="0" t="s">
         <v>158</v>
@@ -8185,11 +8995,11 @@
       <c r="A443" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B443" s="0">
-        <v>2</v>
+      <c r="B443" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C443" s="0" t="s">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="D443" s="0" t="s">
         <v>158</v>
@@ -8202,11 +9012,11 @@
       <c r="A444" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B444" s="0">
-        <v>3</v>
+      <c r="B444" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C444" s="0" t="s">
-        <v>162</v>
+        <v>454</v>
       </c>
       <c r="D444" s="0" t="s">
         <v>158</v>
@@ -8219,11 +9029,11 @@
       <c r="A445" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B445" s="0">
-        <v>3</v>
+      <c r="B445" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C445" s="0" t="s">
-        <v>162</v>
+        <v>454</v>
       </c>
       <c r="D445" s="0" t="s">
         <v>158</v>
@@ -8236,11 +9046,11 @@
       <c r="A446" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B446" s="0">
-        <v>3</v>
+      <c r="B446" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C446" s="0" t="s">
-        <v>162</v>
+        <v>454</v>
       </c>
       <c r="D446" s="0" t="s">
         <v>158</v>
@@ -8253,11 +9063,11 @@
       <c r="A447" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B447" s="0">
-        <v>3</v>
+      <c r="B447" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C447" s="0" t="s">
-        <v>162</v>
+        <v>454</v>
       </c>
       <c r="D447" s="0" t="s">
         <v>158</v>
@@ -8270,11 +9080,11 @@
       <c r="A448" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B448" s="0">
-        <v>3</v>
+      <c r="B448" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C448" s="0" t="s">
-        <v>162</v>
+        <v>454</v>
       </c>
       <c r="D448" s="0" t="s">
         <v>158</v>
@@ -8287,11 +9097,11 @@
       <c r="A449" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B449" s="0">
-        <v>4</v>
+      <c r="B449" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C449" s="0" t="s">
-        <v>162</v>
+        <v>455</v>
       </c>
       <c r="D449" s="0" t="s">
         <v>158</v>
@@ -8304,11 +9114,11 @@
       <c r="A450" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B450" s="0">
-        <v>4</v>
+      <c r="B450" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C450" s="0" t="s">
-        <v>162</v>
+        <v>455</v>
       </c>
       <c r="D450" s="0" t="s">
         <v>158</v>
@@ -8321,11 +9131,11 @@
       <c r="A451" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B451" s="0">
-        <v>4</v>
+      <c r="B451" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C451" s="0" t="s">
-        <v>162</v>
+        <v>455</v>
       </c>
       <c r="D451" s="0" t="s">
         <v>158</v>
@@ -8338,11 +9148,11 @@
       <c r="A452" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="B452" s="0">
-        <v>4</v>
+      <c r="B452" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C452" s="0" t="s">
-        <v>162</v>
+        <v>455</v>
       </c>
       <c r="D452" s="0" t="s">
         <v>158</v>
@@ -8355,11 +9165,11 @@
       <c r="A453" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="B453" s="0">
-        <v>1</v>
+      <c r="B453" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C453" s="0" t="s">
-        <v>162</v>
+        <v>456</v>
       </c>
       <c r="D453" s="0" t="s">
         <v>158</v>
@@ -8372,11 +9182,11 @@
       <c r="A454" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="B454" s="0">
-        <v>4</v>
+      <c r="B454" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C454" s="0" t="s">
-        <v>162</v>
+        <v>457</v>
       </c>
       <c r="D454" s="0" t="s">
         <v>158</v>
@@ -8389,11 +9199,11 @@
       <c r="A455" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="B455" s="0">
-        <v>4</v>
+      <c r="B455" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C455" s="0" t="s">
-        <v>162</v>
+        <v>457</v>
       </c>
       <c r="D455" s="0" t="s">
         <v>158</v>
@@ -8406,11 +9216,11 @@
       <c r="A456" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B456" s="0">
-        <v>2</v>
+      <c r="B456" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C456" s="0" t="s">
-        <v>162</v>
+        <v>458</v>
       </c>
       <c r="D456" s="0" t="s">
         <v>158</v>
@@ -8423,11 +9233,11 @@
       <c r="A457" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B457" s="0">
-        <v>2</v>
+      <c r="B457" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C457" s="0" t="s">
-        <v>162</v>
+        <v>458</v>
       </c>
       <c r="D457" s="0" t="s">
         <v>158</v>
@@ -8440,11 +9250,11 @@
       <c r="A458" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B458" s="0">
-        <v>3</v>
+      <c r="B458" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C458" s="0" t="s">
-        <v>162</v>
+        <v>459</v>
       </c>
       <c r="D458" s="0" t="s">
         <v>158</v>
@@ -8457,11 +9267,11 @@
       <c r="A459" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B459" s="0">
-        <v>3</v>
+      <c r="B459" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C459" s="0" t="s">
-        <v>162</v>
+        <v>459</v>
       </c>
       <c r="D459" s="0" t="s">
         <v>158</v>
@@ -8474,11 +9284,11 @@
       <c r="A460" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B460" s="0">
-        <v>3</v>
+      <c r="B460" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C460" s="0" t="s">
-        <v>162</v>
+        <v>459</v>
       </c>
       <c r="D460" s="0" t="s">
         <v>158</v>
@@ -8491,11 +9301,11 @@
       <c r="A461" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B461" s="0">
-        <v>3</v>
+      <c r="B461" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C461" s="0" t="s">
-        <v>162</v>
+        <v>459</v>
       </c>
       <c r="D461" s="0" t="s">
         <v>158</v>
@@ -8508,11 +9318,11 @@
       <c r="A462" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="B462" s="0">
-        <v>3</v>
+      <c r="B462" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C462" s="0" t="s">
-        <v>162</v>
+        <v>459</v>
       </c>
       <c r="D462" s="0" t="s">
         <v>158</v>
@@ -8525,11 +9335,11 @@
       <c r="A463" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B463" s="0">
-        <v>2</v>
+      <c r="B463" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C463" s="0" t="s">
-        <v>162</v>
+        <v>460</v>
       </c>
       <c r="D463" s="0" t="s">
         <v>158</v>
@@ -8542,11 +9352,11 @@
       <c r="A464" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B464" s="0">
-        <v>3</v>
+      <c r="B464" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C464" s="0" t="s">
-        <v>162</v>
+        <v>461</v>
       </c>
       <c r="D464" s="0" t="s">
         <v>158</v>
@@ -8559,11 +9369,11 @@
       <c r="A465" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B465" s="0">
-        <v>3</v>
+      <c r="B465" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C465" s="0" t="s">
-        <v>162</v>
+        <v>461</v>
       </c>
       <c r="D465" s="0" t="s">
         <v>158</v>
@@ -8576,11 +9386,11 @@
       <c r="A466" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B466" s="0">
-        <v>3</v>
+      <c r="B466" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C466" s="0" t="s">
-        <v>162</v>
+        <v>461</v>
       </c>
       <c r="D466" s="0" t="s">
         <v>158</v>
@@ -8593,11 +9403,11 @@
       <c r="A467" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B467" s="0">
-        <v>3</v>
+      <c r="B467" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C467" s="0" t="s">
-        <v>162</v>
+        <v>461</v>
       </c>
       <c r="D467" s="0" t="s">
         <v>158</v>
@@ -8610,11 +9420,11 @@
       <c r="A468" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B468" s="0">
-        <v>3</v>
+      <c r="B468" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C468" s="0" t="s">
-        <v>162</v>
+        <v>461</v>
       </c>
       <c r="D468" s="0" t="s">
         <v>158</v>
@@ -8627,11 +9437,11 @@
       <c r="A469" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B469" s="0">
-        <v>3</v>
+      <c r="B469" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C469" s="0" t="s">
-        <v>162</v>
+        <v>461</v>
       </c>
       <c r="D469" s="0" t="s">
         <v>158</v>
@@ -8644,11 +9454,11 @@
       <c r="A470" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="B470" s="0">
-        <v>4</v>
+      <c r="B470" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C470" s="0" t="s">
-        <v>162</v>
+        <v>462</v>
       </c>
       <c r="D470" s="0" t="s">
         <v>158</v>
@@ -8661,11 +9471,11 @@
       <c r="A471" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B471" s="0">
-        <v>2</v>
+      <c r="B471" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C471" s="0" t="s">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="D471" s="0" t="s">
         <v>158</v>
@@ -8678,11 +9488,11 @@
       <c r="A472" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B472" s="0">
-        <v>2</v>
+      <c r="B472" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C472" s="0" t="s">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="D472" s="0" t="s">
         <v>158</v>
@@ -8695,11 +9505,11 @@
       <c r="A473" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B473" s="0">
-        <v>2</v>
+      <c r="B473" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C473" s="0" t="s">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="D473" s="0" t="s">
         <v>158</v>
@@ -8712,11 +9522,11 @@
       <c r="A474" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B474" s="0">
-        <v>2</v>
+      <c r="B474" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C474" s="0" t="s">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="D474" s="0" t="s">
         <v>158</v>
@@ -8729,11 +9539,11 @@
       <c r="A475" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B475" s="0">
-        <v>3</v>
+      <c r="B475" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C475" s="0" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="D475" s="0" t="s">
         <v>158</v>
@@ -8746,11 +9556,11 @@
       <c r="A476" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B476" s="0">
-        <v>3</v>
+      <c r="B476" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C476" s="0" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="D476" s="0" t="s">
         <v>158</v>
@@ -8763,11 +9573,11 @@
       <c r="A477" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B477" s="0">
-        <v>3</v>
+      <c r="B477" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C477" s="0" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="D477" s="0" t="s">
         <v>158</v>
@@ -8780,11 +9590,11 @@
       <c r="A478" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B478" s="0">
-        <v>3</v>
+      <c r="B478" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C478" s="0" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="D478" s="0" t="s">
         <v>158</v>
@@ -8797,11 +9607,11 @@
       <c r="A479" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B479" s="0">
-        <v>3</v>
+      <c r="B479" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C479" s="0" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="D479" s="0" t="s">
         <v>158</v>
@@ -8814,11 +9624,11 @@
       <c r="A480" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B480" s="0">
-        <v>3</v>
+      <c r="B480" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C480" s="0" t="s">
-        <v>162</v>
+        <v>464</v>
       </c>
       <c r="D480" s="0" t="s">
         <v>158</v>
@@ -8831,11 +9641,11 @@
       <c r="A481" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B481" s="0">
-        <v>4</v>
+      <c r="B481" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C481" s="0" t="s">
-        <v>162</v>
+        <v>465</v>
       </c>
       <c r="D481" s="0" t="s">
         <v>158</v>
@@ -8848,11 +9658,11 @@
       <c r="A482" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="B482" s="0">
-        <v>4</v>
+      <c r="B482" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C482" s="0" t="s">
-        <v>162</v>
+        <v>465</v>
       </c>
       <c r="D482" s="0" t="s">
         <v>158</v>
@@ -8865,11 +9675,11 @@
       <c r="A483" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B483" s="0">
-        <v>4</v>
+      <c r="B483" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C483" s="0" t="s">
-        <v>162</v>
+        <v>466</v>
       </c>
       <c r="D483" s="0" t="s">
         <v>158</v>
@@ -8882,11 +9692,11 @@
       <c r="A484" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B484" s="0">
-        <v>4</v>
+      <c r="B484" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C484" s="0" t="s">
-        <v>162</v>
+        <v>466</v>
       </c>
       <c r="D484" s="0" t="s">
         <v>158</v>
@@ -8899,11 +9709,11 @@
       <c r="A485" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="B485" s="0">
-        <v>4</v>
+      <c r="B485" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C485" s="0" t="s">
-        <v>162</v>
+        <v>466</v>
       </c>
       <c r="D485" s="0" t="s">
         <v>158</v>
@@ -8916,11 +9726,11 @@
       <c r="A486" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B486" s="0">
-        <v>1</v>
+      <c r="B486" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C486" s="0" t="s">
-        <v>162</v>
+        <v>467</v>
       </c>
       <c r="D486" s="0" t="s">
         <v>158</v>
@@ -8933,11 +9743,11 @@
       <c r="A487" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B487" s="0">
-        <v>1</v>
+      <c r="B487" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C487" s="0" t="s">
-        <v>162</v>
+        <v>467</v>
       </c>
       <c r="D487" s="0" t="s">
         <v>158</v>
@@ -8950,11 +9760,11 @@
       <c r="A488" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B488" s="0">
-        <v>1</v>
+      <c r="B488" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C488" s="0" t="s">
-        <v>162</v>
+        <v>467</v>
       </c>
       <c r="D488" s="0" t="s">
         <v>158</v>
@@ -8967,11 +9777,11 @@
       <c r="A489" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B489" s="0">
-        <v>2</v>
+      <c r="B489" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C489" s="0" t="s">
-        <v>162</v>
+        <v>468</v>
       </c>
       <c r="D489" s="0" t="s">
         <v>158</v>
@@ -8984,11 +9794,11 @@
       <c r="A490" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B490" s="0">
-        <v>2</v>
+      <c r="B490" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C490" s="0" t="s">
-        <v>162</v>
+        <v>468</v>
       </c>
       <c r="D490" s="0" t="s">
         <v>158</v>
@@ -9001,11 +9811,11 @@
       <c r="A491" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B491" s="0">
-        <v>2</v>
+      <c r="B491" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C491" s="0" t="s">
-        <v>162</v>
+        <v>468</v>
       </c>
       <c r="D491" s="0" t="s">
         <v>158</v>
@@ -9018,11 +9828,11 @@
       <c r="A492" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B492" s="0">
-        <v>2</v>
+      <c r="B492" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C492" s="0" t="s">
-        <v>162</v>
+        <v>468</v>
       </c>
       <c r="D492" s="0" t="s">
         <v>158</v>
@@ -9035,11 +9845,11 @@
       <c r="A493" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B493" s="0">
-        <v>3</v>
+      <c r="B493" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C493" s="0" t="s">
-        <v>162</v>
+        <v>469</v>
       </c>
       <c r="D493" s="0" t="s">
         <v>158</v>
@@ -9052,11 +9862,11 @@
       <c r="A494" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B494" s="0">
-        <v>3</v>
+      <c r="B494" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C494" s="0" t="s">
-        <v>162</v>
+        <v>469</v>
       </c>
       <c r="D494" s="0" t="s">
         <v>158</v>
@@ -9069,11 +9879,11 @@
       <c r="A495" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B495" s="0">
-        <v>4</v>
+      <c r="B495" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C495" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D495" s="0" t="s">
         <v>158</v>
@@ -9086,11 +9896,11 @@
       <c r="A496" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B496" s="0">
-        <v>4</v>
+      <c r="B496" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C496" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D496" s="0" t="s">
         <v>158</v>
@@ -9103,11 +9913,11 @@
       <c r="A497" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B497" s="0">
-        <v>4</v>
+      <c r="B497" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C497" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D497" s="0" t="s">
         <v>158</v>
@@ -9120,11 +9930,11 @@
       <c r="A498" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B498" s="0">
-        <v>4</v>
+      <c r="B498" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C498" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D498" s="0" t="s">
         <v>158</v>
@@ -9137,11 +9947,11 @@
       <c r="A499" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B499" s="0">
-        <v>4</v>
+      <c r="B499" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C499" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D499" s="0" t="s">
         <v>158</v>
@@ -9154,11 +9964,11 @@
       <c r="A500" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B500" s="0">
-        <v>4</v>
+      <c r="B500" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C500" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D500" s="0" t="s">
         <v>158</v>
@@ -9171,11 +9981,11 @@
       <c r="A501" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B501" s="0">
-        <v>4</v>
+      <c r="B501" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C501" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D501" s="0" t="s">
         <v>158</v>
@@ -9188,11 +9998,11 @@
       <c r="A502" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="B502" s="0">
-        <v>4</v>
+      <c r="B502" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C502" s="0" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="D502" s="0" t="s">
         <v>158</v>
@@ -9205,11 +10015,11 @@
       <c r="A503" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B503" s="0">
-        <v>1</v>
+      <c r="B503" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C503" s="0" t="s">
-        <v>162</v>
+        <v>471</v>
       </c>
       <c r="D503" s="0" t="s">
         <v>158</v>
@@ -9222,11 +10032,11 @@
       <c r="A504" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B504" s="0">
-        <v>1</v>
+      <c r="B504" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C504" s="0" t="s">
-        <v>162</v>
+        <v>471</v>
       </c>
       <c r="D504" s="0" t="s">
         <v>158</v>
@@ -9239,11 +10049,11 @@
       <c r="A505" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B505" s="0">
-        <v>1</v>
+      <c r="B505" s="0" t="s">
+        <v>123</v>
       </c>
       <c r="C505" s="0" t="s">
-        <v>162</v>
+        <v>471</v>
       </c>
       <c r="D505" s="0" t="s">
         <v>158</v>
@@ -9256,11 +10066,11 @@
       <c r="A506" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B506" s="0">
-        <v>2</v>
+      <c r="B506" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C506" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D506" s="0" t="s">
         <v>158</v>
@@ -9273,11 +10083,11 @@
       <c r="A507" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B507" s="0">
-        <v>2</v>
+      <c r="B507" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C507" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D507" s="0" t="s">
         <v>158</v>
@@ -9290,11 +10100,11 @@
       <c r="A508" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B508" s="0">
-        <v>2</v>
+      <c r="B508" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C508" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D508" s="0" t="s">
         <v>158</v>
@@ -9307,11 +10117,11 @@
       <c r="A509" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B509" s="0">
-        <v>2</v>
+      <c r="B509" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C509" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D509" s="0" t="s">
         <v>158</v>
@@ -9324,11 +10134,11 @@
       <c r="A510" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B510" s="0">
-        <v>2</v>
+      <c r="B510" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C510" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D510" s="0" t="s">
         <v>158</v>
@@ -9341,11 +10151,11 @@
       <c r="A511" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B511" s="0">
-        <v>2</v>
+      <c r="B511" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C511" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D511" s="0" t="s">
         <v>158</v>
@@ -9358,11 +10168,11 @@
       <c r="A512" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B512" s="0">
-        <v>2</v>
+      <c r="B512" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C512" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D512" s="0" t="s">
         <v>158</v>
@@ -9375,11 +10185,11 @@
       <c r="A513" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B513" s="0">
-        <v>2</v>
+      <c r="B513" s="0" t="s">
+        <v>205</v>
       </c>
       <c r="C513" s="0" t="s">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="D513" s="0" t="s">
         <v>158</v>
@@ -9392,11 +10202,11 @@
       <c r="A514" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B514" s="0">
-        <v>3</v>
+      <c r="B514" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C514" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D514" s="0" t="s">
         <v>158</v>
@@ -9409,11 +10219,11 @@
       <c r="A515" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B515" s="0">
-        <v>3</v>
+      <c r="B515" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C515" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D515" s="0" t="s">
         <v>158</v>
@@ -9426,11 +10236,11 @@
       <c r="A516" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B516" s="0">
-        <v>3</v>
+      <c r="B516" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C516" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D516" s="0" t="s">
         <v>158</v>
@@ -9443,11 +10253,11 @@
       <c r="A517" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B517" s="0">
-        <v>3</v>
+      <c r="B517" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C517" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D517" s="0" t="s">
         <v>158</v>
@@ -9460,11 +10270,11 @@
       <c r="A518" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B518" s="0">
-        <v>3</v>
+      <c r="B518" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C518" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D518" s="0" t="s">
         <v>158</v>
@@ -9477,11 +10287,11 @@
       <c r="A519" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B519" s="0">
-        <v>3</v>
+      <c r="B519" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C519" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D519" s="0" t="s">
         <v>158</v>
@@ -9494,11 +10304,11 @@
       <c r="A520" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B520" s="0">
-        <v>3</v>
+      <c r="B520" s="0" t="s">
+        <v>206</v>
       </c>
       <c r="C520" s="0" t="s">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="D520" s="0" t="s">
         <v>158</v>
@@ -9511,11 +10321,11 @@
       <c r="A521" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B521" s="0">
-        <v>4</v>
+      <c r="B521" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C521" s="0" t="s">
-        <v>162</v>
+        <v>474</v>
       </c>
       <c r="D521" s="0" t="s">
         <v>158</v>
@@ -9528,11 +10338,11 @@
       <c r="A522" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B522" s="0">
-        <v>4</v>
+      <c r="B522" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C522" s="0" t="s">
-        <v>162</v>
+        <v>474</v>
       </c>
       <c r="D522" s="0" t="s">
         <v>158</v>
@@ -9545,11 +10355,11 @@
       <c r="A523" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B523" s="0">
-        <v>4</v>
+      <c r="B523" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C523" s="0" t="s">
-        <v>162</v>
+        <v>474</v>
       </c>
       <c r="D523" s="0" t="s">
         <v>158</v>
@@ -9562,11 +10372,11 @@
       <c r="A524" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="B524" s="0">
-        <v>4</v>
+      <c r="B524" s="0" t="s">
+        <v>207</v>
       </c>
       <c r="C524" s="0" t="s">
-        <v>162</v>
+        <v>474</v>
       </c>
       <c r="D524" s="0" t="s">
         <v>158</v>
